--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,16 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545083EC-BDF7-49C2-BE79-DF51BE21346B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DB8AA6-D9BD-47DD-870B-8E672E0FE850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="10" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash Fill" sheetId="1" r:id="rId1"/>
     <sheet name="Paste Special" sheetId="2" r:id="rId2"/>
     <sheet name="Text To Column" sheetId="3" r:id="rId3"/>
     <sheet name="Fill Series" sheetId="4" r:id="rId4"/>
+    <sheet name="formatting" sheetId="6" r:id="rId5"/>
+    <sheet name="Sorting" sheetId="7" r:id="rId6"/>
+    <sheet name="Filteering" sheetId="8" r:id="rId7"/>
+    <sheet name="Arithmatic" sheetId="9" r:id="rId8"/>
+    <sheet name="Text Functions" sheetId="10" r:id="rId9"/>
+    <sheet name="Logical Functions" sheetId="11" r:id="rId10"/>
+    <sheet name="Date and Time Func" sheetId="12" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Filteering!$A$1:$E$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -82,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="342">
   <si>
     <t>Mohan</t>
   </si>
@@ -688,13 +698,437 @@
   </si>
   <si>
     <t>bhadauriya</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Sub-Category</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Payment Mode</t>
+  </si>
+  <si>
+    <t>Dates</t>
+  </si>
+  <si>
+    <t>1st Jan 2023</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Zomato</t>
+  </si>
+  <si>
+    <t>UPI</t>
+  </si>
+  <si>
+    <t>Clothes</t>
+  </si>
+  <si>
+    <t>Dress</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>2nd Jan 2023</t>
+  </si>
+  <si>
+    <t>Grocery</t>
+  </si>
+  <si>
+    <t>Fruits and Veggies</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Milk</t>
+  </si>
+  <si>
+    <t>4th Jan 2023</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>5th Jan 2023</t>
+  </si>
+  <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
+    <t>6th Jan 2023</t>
+  </si>
+  <si>
+    <t>7th Jan 2023</t>
+  </si>
+  <si>
+    <t>Bills</t>
+  </si>
+  <si>
+    <t>House Rent</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>8th Jan 2023</t>
+  </si>
+  <si>
+    <t>Essentials</t>
+  </si>
+  <si>
+    <t>Shampoo</t>
+  </si>
+  <si>
+    <t>9th Jan 2023</t>
+  </si>
+  <si>
+    <t>10th Jan 2023</t>
+  </si>
+  <si>
+    <t>Diary</t>
+  </si>
+  <si>
+    <t>Chai</t>
+  </si>
+  <si>
+    <t>11th Jan 2023</t>
+  </si>
+  <si>
+    <t>12th Jan 2023</t>
+  </si>
+  <si>
+    <t>Cylinder</t>
+  </si>
+  <si>
+    <t>Salt and Sugar</t>
+  </si>
+  <si>
+    <t>13th Jan 2023</t>
+  </si>
+  <si>
+    <t>14th Jan 2023</t>
+  </si>
+  <si>
+    <t>Food Oil</t>
+  </si>
+  <si>
+    <t>15th Jan 2023</t>
+  </si>
+  <si>
+    <t>Bread and Milk</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Qty Ordered</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>Discount Amt</t>
+  </si>
+  <si>
+    <t>Total Cost (Formula)</t>
+  </si>
+  <si>
+    <t>Net Price after Disc (Formula)</t>
+  </si>
+  <si>
+    <t>Per Item Cost (Formula)</t>
+  </si>
+  <si>
+    <t>Smartphone</t>
+  </si>
+  <si>
+    <t>Wireless Mouse</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Addition</t>
+  </si>
+  <si>
+    <t>Multiplication</t>
+  </si>
+  <si>
+    <t>Substraction</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Concatenate</t>
+  </si>
+  <si>
+    <t>Lower</t>
+  </si>
+  <si>
+    <t>Upper</t>
+  </si>
+  <si>
+    <t>Proper</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>MR.</t>
+  </si>
+  <si>
+    <t>MS.</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
+  <si>
+    <t>MRS.</t>
+  </si>
+  <si>
+    <t>JACQUELY</t>
+  </si>
+  <si>
+    <t>LAI</t>
+  </si>
+  <si>
+    <t>Find</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
+  <si>
+    <t>Substitution</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Hire Date</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Conditions</t>
+  </si>
+  <si>
+    <t>If</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>Emily Davis</t>
+  </si>
+  <si>
+    <t>Sr. Manger</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Theodore Dinh</t>
+  </si>
+  <si>
+    <t>Technical Architect</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Luna Sanders</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Penelope Jordan</t>
+  </si>
+  <si>
+    <t>Computer Systems Manager</t>
+  </si>
+  <si>
+    <t>Austin Vo</t>
+  </si>
+  <si>
+    <t>Sr. Analyst</t>
+  </si>
+  <si>
+    <t>Joshua Gupta</t>
+  </si>
+  <si>
+    <t>Account Representative</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Ruby Barnes</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>Luke Martin</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>Easton Bailey</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>Madeline Walker</t>
+  </si>
+  <si>
+    <t>Savannah Ali</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Camila Rogers</t>
+  </si>
+  <si>
+    <t>Controls Engineer</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Eli Jones</t>
+  </si>
+  <si>
+    <t>Everleigh Ng</t>
+  </si>
+  <si>
+    <t>Robert Yang</t>
+  </si>
+  <si>
+    <t>Isabella Xi</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Bella Powell</t>
+  </si>
+  <si>
+    <t>Camila Silva</t>
+  </si>
+  <si>
+    <t>David Barnes</t>
+  </si>
+  <si>
+    <t>Today</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Now</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>Mins</t>
+  </si>
+  <si>
+    <t>Sec</t>
+  </si>
+  <si>
+    <t>date + 3days</t>
+  </si>
+  <si>
+    <t>date + 3months</t>
+  </si>
+  <si>
+    <t>date +3years</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -736,16 +1170,32 @@
       <name val="Google Sans Text"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -762,7 +1212,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -800,11 +1250,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -819,9 +1278,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
@@ -834,16 +1290,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -855,11 +1311,72 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -876,6 +1393,36 @@
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="ankit gujre" id="{1B580FBE-5650-4AF0-8974-B47F26D25219}" userId="989b8d879cf27b87" providerId="Windows Live"/>
 </personList>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6CCC87F7-49FC-4487-B888-0F204218EFD5}" name="Table3" displayName="Table3" ref="A1:E20" totalsRowShown="0">
+  <autoFilter ref="A1:E20" xr:uid="{6CCC87F7-49FC-4487-B888-0F204218EFD5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
+    <sortCondition descending="1" ref="D2:D20"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{5F31884B-E010-4818-8F32-51B32263D520}" name="Date"/>
+    <tableColumn id="2" xr3:uid="{397BBE4B-2491-4FC6-A09E-5B46B3703C0B}" name="Category"/>
+    <tableColumn id="3" xr3:uid="{5056282D-8BF3-45E8-BCDD-03E7D521660E}" name="Sub-Category"/>
+    <tableColumn id="4" xr3:uid="{CDD4DBC2-9D0E-4997-BE82-5467F16E1875}" name="Amount"/>
+    <tableColumn id="5" xr3:uid="{8770A22C-7CD0-4F30-A39F-69F4460B03B8}" name="Payment Mode"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B24B5EE4-B8ED-4CEE-9BEA-CD8D02069132}" name="Table4" displayName="Table4" ref="H1:H20" totalsRowShown="0">
+  <autoFilter ref="H1:H20" xr:uid="{B24B5EE4-B8ED-4CEE-9BEA-CD8D02069132}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H2:H20">
+    <sortCondition ref="H1:H20"/>
+  </sortState>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{245ABA7D-7ECE-4568-A31E-1E8B7C978F00}" name="Dates" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1353,46 +1900,898 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="F9:J13"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D07DC63-C3FE-41CA-A5CC-04D4B9D96094}">
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="31" customFormat="1">
+      <c r="A1" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="K1" s="31" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2">
+        <v>55</v>
+      </c>
+      <c r="F2" s="18">
+        <v>42468</v>
+      </c>
+      <c r="G2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H2" t="b">
+        <f>E2&gt;50</f>
+        <v>1</v>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(E2&gt;50,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="J2" t="str">
+        <f>IF(AND(C2="IT",G2="United States"),"Included","Excluded")</f>
+        <v>Included</v>
+      </c>
+      <c r="K2" t="str">
+        <f>IF(OR(D2="Female",G3="China"),"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3">
+        <v>59</v>
+      </c>
+      <c r="F3" s="18">
+        <v>35763</v>
+      </c>
+      <c r="G3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H3" t="b">
+        <f t="shared" ref="H3:H20" si="0">E3&gt;50</f>
+        <v>1</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I20" si="1">IF(E3&gt;50,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J20" si="2">IF(AND(C3="IT",G3="United States"),"Included","Excluded")</f>
+        <v>Excluded</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K20" si="3">IF(OR(D3="Female",G4="China"),"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4" s="18">
+        <v>39016</v>
+      </c>
+      <c r="G4" t="s">
+        <v>295</v>
+      </c>
+      <c r="H4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E5">
+        <v>26</v>
+      </c>
+      <c r="F5" s="18">
+        <v>43735</v>
+      </c>
+      <c r="G5" t="s">
+        <v>295</v>
+      </c>
+      <c r="H5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="2"/>
+        <v>Included</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D6" t="s">
+        <v>298</v>
+      </c>
+      <c r="E6">
+        <v>55</v>
+      </c>
+      <c r="F6" s="18">
+        <v>35023</v>
+      </c>
+      <c r="G6" t="s">
+        <v>295</v>
+      </c>
+      <c r="H6" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7" s="18">
+        <v>42759</v>
+      </c>
+      <c r="G7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H7" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E8">
+        <v>27</v>
+      </c>
+      <c r="F8" s="18">
+        <v>44013</v>
+      </c>
+      <c r="G8" t="s">
+        <v>295</v>
+      </c>
+      <c r="H8" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="2"/>
+        <v>Included</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9" s="18">
+        <v>43967</v>
+      </c>
+      <c r="G9" t="s">
+        <v>295</v>
+      </c>
+      <c r="H9" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10">
+        <v>29</v>
+      </c>
+      <c r="F10" s="18">
+        <v>43490</v>
+      </c>
+      <c r="G10" t="s">
+        <v>295</v>
+      </c>
+      <c r="H10" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D11" t="s">
+        <v>294</v>
+      </c>
+      <c r="E11">
+        <v>34</v>
+      </c>
+      <c r="F11" s="18">
+        <v>43264</v>
+      </c>
+      <c r="G11" t="s">
+        <v>295</v>
+      </c>
+      <c r="H11" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" t="s">
+        <v>318</v>
+      </c>
+      <c r="D12" t="s">
+        <v>294</v>
+      </c>
+      <c r="E12">
+        <v>36</v>
+      </c>
+      <c r="F12" s="18">
+        <v>39855</v>
+      </c>
+      <c r="G12" t="s">
+        <v>295</v>
+      </c>
+      <c r="H12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>319</v>
+      </c>
+      <c r="B13" t="s">
+        <v>320</v>
+      </c>
+      <c r="C13" t="s">
+        <v>321</v>
+      </c>
+      <c r="D13" t="s">
+        <v>294</v>
+      </c>
+      <c r="E13">
+        <v>27</v>
+      </c>
+      <c r="F13" s="18">
+        <v>44490</v>
+      </c>
+      <c r="G13" t="s">
+        <v>295</v>
+      </c>
+      <c r="H13" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>322</v>
+      </c>
+      <c r="B14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C14" t="s">
+        <v>318</v>
+      </c>
+      <c r="D14" t="s">
+        <v>298</v>
+      </c>
+      <c r="E14">
+        <v>59</v>
+      </c>
+      <c r="F14" s="18">
+        <v>36233</v>
+      </c>
+      <c r="G14" t="s">
+        <v>295</v>
+      </c>
+      <c r="H14" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>323</v>
+      </c>
+      <c r="B15" t="s">
+        <v>292</v>
+      </c>
+      <c r="C15" t="s">
+        <v>302</v>
+      </c>
+      <c r="D15" t="s">
+        <v>294</v>
+      </c>
+      <c r="E15">
+        <v>51</v>
+      </c>
+      <c r="F15" s="18">
+        <v>44357</v>
+      </c>
+      <c r="G15" t="s">
+        <v>299</v>
+      </c>
+      <c r="H15" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" t="s">
+        <v>315</v>
+      </c>
+      <c r="D16" t="s">
+        <v>298</v>
+      </c>
+      <c r="E16">
+        <v>31</v>
+      </c>
+      <c r="F16" s="18">
+        <v>43043</v>
+      </c>
+      <c r="G16" t="s">
+        <v>295</v>
+      </c>
+      <c r="H16" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>325</v>
+      </c>
+      <c r="B17" t="s">
+        <v>326</v>
+      </c>
+      <c r="C17" t="s">
+        <v>327</v>
+      </c>
+      <c r="D17" t="s">
+        <v>294</v>
+      </c>
+      <c r="E17">
+        <v>41</v>
+      </c>
+      <c r="F17" s="18">
+        <v>41346</v>
+      </c>
+      <c r="G17" t="s">
+        <v>295</v>
+      </c>
+      <c r="H17" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="1"/>
+        <v>Junior</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>328</v>
+      </c>
+      <c r="B18" t="s">
+        <v>301</v>
+      </c>
+      <c r="C18" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" t="s">
+        <v>294</v>
+      </c>
+      <c r="E18">
+        <v>65</v>
+      </c>
+      <c r="F18" s="18">
+        <v>37319</v>
+      </c>
+      <c r="G18" t="s">
+        <v>295</v>
+      </c>
+      <c r="H18" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B19" t="s">
+        <v>292</v>
+      </c>
+      <c r="C19" t="s">
+        <v>327</v>
+      </c>
+      <c r="D19" t="s">
+        <v>294</v>
+      </c>
+      <c r="E19">
+        <v>64</v>
+      </c>
+      <c r="F19" s="18">
+        <v>37956</v>
+      </c>
+      <c r="G19" t="s">
+        <v>295</v>
+      </c>
+      <c r="H19" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="2"/>
+        <v>Excluded</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="3"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>330</v>
+      </c>
+      <c r="B20" t="s">
+        <v>301</v>
+      </c>
+      <c r="C20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D20" t="s">
+        <v>298</v>
+      </c>
+      <c r="E20">
+        <v>64</v>
+      </c>
+      <c r="F20" s="18">
+        <v>41581</v>
+      </c>
+      <c r="G20" t="s">
+        <v>295</v>
+      </c>
+      <c r="H20" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="1"/>
+        <v>Senior</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="2"/>
+        <v>Included</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="3"/>
+        <v>No</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EC6E42-5F38-4262-90E2-276AAD0D4F4E}">
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="31" t="s">
+        <v>331</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>336</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="K1" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="L1" s="31" t="s">
+        <v>341</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1439,19 +2838,19 @@
       <c r="E1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1472,19 +2871,19 @@
         <f>SUM(B2:D2)</f>
         <v>22000</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="7">
         <v>5000</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="7">
         <v>12000</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="7">
         <v>5000</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="8">
         <f>SUM(I2:K2)</f>
         <v>22000</v>
       </c>
@@ -1503,22 +2902,22 @@
         <v>600</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E12" si="0">SUM(B3:D3)</f>
+        <f t="shared" ref="E3:E11" si="0">SUM(B3:D3)</f>
         <v>1800</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="7">
         <v>600</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="7">
         <v>600</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="7">
         <v>600</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="8">
         <f t="shared" ref="L3:L11" si="1">SUM(I3:K3)</f>
         <v>1800</v>
       </c>
@@ -1576,19 +2975,19 @@
         <f t="shared" si="0"/>
         <v>10150</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <v>5000</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="7">
         <v>5000</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
         <v>150</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="8">
         <f t="shared" si="1"/>
         <v>10150</v>
       </c>
@@ -1644,19 +3043,19 @@
         <f t="shared" si="0"/>
         <v>450</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>150</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="7">
         <v>150</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>150</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
@@ -1712,19 +3111,19 @@
         <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>6000</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <v>6000</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <v>6000</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="8">
         <f t="shared" si="1"/>
         <v>18000</v>
       </c>
@@ -1780,19 +3179,19 @@
         <f t="shared" si="0"/>
         <v>177</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <v>59</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="7">
         <v>59</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="7">
         <v>59</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="8">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
@@ -1800,43 +3199,43 @@
         <v>29</v>
       </c>
       <c r="O7" s="3">
-        <f>SUM(O4:O6)</f>
+        <f t="shared" ref="O7:X7" si="2">SUM(O4:O6)</f>
         <v>22000</v>
       </c>
       <c r="P7" s="3">
-        <f>SUM(P4:P6)</f>
+        <f t="shared" si="2"/>
         <v>1800</v>
       </c>
       <c r="Q7" s="3">
-        <f>SUM(Q4:Q6)</f>
+        <f t="shared" si="2"/>
         <v>10150</v>
       </c>
       <c r="R7" s="3">
-        <f>SUM(R4:R6)</f>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="S7" s="3">
-        <f>SUM(S4:S6)</f>
+        <f t="shared" si="2"/>
         <v>18000</v>
       </c>
       <c r="T7" s="3">
-        <f>SUM(T4:T6)</f>
+        <f t="shared" si="2"/>
         <v>177</v>
       </c>
       <c r="U7" s="3">
-        <f>SUM(U4:U6)</f>
+        <f t="shared" si="2"/>
         <v>4500</v>
       </c>
       <c r="V7" s="3">
-        <f>SUM(V4:V6)</f>
+        <f t="shared" si="2"/>
         <v>1680</v>
       </c>
       <c r="W7" s="3">
-        <f>SUM(W4:W6)</f>
+        <f t="shared" si="2"/>
         <v>27000</v>
       </c>
       <c r="X7" s="3">
-        <f>SUM(X4:X6)</f>
+        <f t="shared" si="2"/>
         <v>9900</v>
       </c>
       <c r="Y7" s="4">
@@ -1861,19 +3260,19 @@
         <f t="shared" si="0"/>
         <v>4500</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>1500</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <v>1500</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="7">
         <v>1500</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
@@ -1895,19 +3294,19 @@
         <f t="shared" si="0"/>
         <v>1680</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <v>90</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="7">
         <v>90</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="7">
         <v>1500</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="8">
         <f t="shared" si="1"/>
         <v>1680</v>
       </c>
@@ -1929,19 +3328,19 @@
         <f t="shared" si="0"/>
         <v>27000</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="7">
         <v>9000</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="7">
         <v>9000</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="7">
         <v>9000</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="8">
         <f t="shared" si="1"/>
         <v>27000</v>
       </c>
@@ -1963,19 +3362,19 @@
         <f t="shared" si="0"/>
         <v>9900</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <v>3300</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <v>3300</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <v>3300</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="8">
         <f t="shared" si="1"/>
         <v>9900</v>
       </c>
@@ -1991,31 +3390,31 @@
         <f>SUM(E2:E11)</f>
         <v>95657</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="10">
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="9">
         <f>SUM(L2:L11)</f>
         <v>95657</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="27.6">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>29</v>
       </c>
       <c r="H15" t="s">
@@ -2035,19 +3434,19 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>5000</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>12000</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>5000</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <f>SUM(B16:D16)</f>
         <v>22000</v>
       </c>
@@ -2069,20 +3468,20 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>600</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>600</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <v>600</v>
       </c>
-      <c r="E17" s="13">
-        <f t="shared" ref="E17:E25" si="2">SUM(B17:D17)</f>
+      <c r="E17" s="12">
+        <f t="shared" ref="E17:E25" si="3">SUM(B17:D17)</f>
         <v>1800</v>
       </c>
       <c r="H17" t="s">
@@ -2098,25 +3497,25 @@
         <v>600</v>
       </c>
       <c r="L17">
-        <f t="shared" ref="L17:L25" si="3">SUM(I17:K17)</f>
+        <f t="shared" ref="L17:L25" si="4">SUM(I17:K17)</f>
         <v>1800</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>5000</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>5000</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <v>150</v>
       </c>
-      <c r="E18" s="13">
-        <f t="shared" si="2"/>
+      <c r="E18" s="12">
+        <f t="shared" si="3"/>
         <v>10150</v>
       </c>
       <c r="H18" t="s">
@@ -2132,25 +3531,25 @@
         <v>150</v>
       </c>
       <c r="L18">
+        <f t="shared" si="4"/>
+        <v>10150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="11">
+        <v>150</v>
+      </c>
+      <c r="C19" s="11">
+        <v>150</v>
+      </c>
+      <c r="D19" s="11">
+        <v>150</v>
+      </c>
+      <c r="E19" s="12">
         <f t="shared" si="3"/>
-        <v>10150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="12">
-        <v>150</v>
-      </c>
-      <c r="C19" s="12">
-        <v>150</v>
-      </c>
-      <c r="D19" s="12">
-        <v>150</v>
-      </c>
-      <c r="E19" s="13">
-        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="H19" t="s">
@@ -2166,25 +3565,25 @@
         <v>150</v>
       </c>
       <c r="L19">
+        <f t="shared" si="4"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="11">
+        <v>6000</v>
+      </c>
+      <c r="C20" s="11">
+        <v>6000</v>
+      </c>
+      <c r="D20" s="11">
+        <v>6000</v>
+      </c>
+      <c r="E20" s="12">
         <f t="shared" si="3"/>
-        <v>450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="12">
-        <v>6000</v>
-      </c>
-      <c r="C20" s="12">
-        <v>6000</v>
-      </c>
-      <c r="D20" s="12">
-        <v>6000</v>
-      </c>
-      <c r="E20" s="13">
-        <f t="shared" si="2"/>
         <v>18000</v>
       </c>
       <c r="H20" t="s">
@@ -2200,25 +3599,25 @@
         <v>6000</v>
       </c>
       <c r="L20">
+        <f t="shared" si="4"/>
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="11">
+        <v>59</v>
+      </c>
+      <c r="C21" s="11">
+        <v>59</v>
+      </c>
+      <c r="D21" s="11">
+        <v>59</v>
+      </c>
+      <c r="E21" s="12">
         <f t="shared" si="3"/>
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="12">
-        <v>59</v>
-      </c>
-      <c r="C21" s="12">
-        <v>59</v>
-      </c>
-      <c r="D21" s="12">
-        <v>59</v>
-      </c>
-      <c r="E21" s="13">
-        <f t="shared" si="2"/>
         <v>177</v>
       </c>
       <c r="H21" t="s">
@@ -2234,25 +3633,25 @@
         <v>59</v>
       </c>
       <c r="L21">
+        <f t="shared" si="4"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="11">
+        <v>1500</v>
+      </c>
+      <c r="C22" s="11">
+        <v>1500</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="12">
         <f t="shared" si="3"/>
-        <v>177</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="12">
-        <v>1500</v>
-      </c>
-      <c r="C22" s="12">
-        <v>1500</v>
-      </c>
-      <c r="D22" s="12">
-        <v>1500</v>
-      </c>
-      <c r="E22" s="13">
-        <f t="shared" si="2"/>
         <v>4500</v>
       </c>
       <c r="H22" t="s">
@@ -2268,25 +3667,25 @@
         <v>1500</v>
       </c>
       <c r="L22">
+        <f t="shared" si="4"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="11">
+        <v>90</v>
+      </c>
+      <c r="C23" s="11">
+        <v>90</v>
+      </c>
+      <c r="D23" s="11">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="12">
         <f t="shared" si="3"/>
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="12">
-        <v>90</v>
-      </c>
-      <c r="C23" s="12">
-        <v>90</v>
-      </c>
-      <c r="D23" s="12">
-        <v>1500</v>
-      </c>
-      <c r="E23" s="13">
-        <f t="shared" si="2"/>
         <v>1680</v>
       </c>
       <c r="H23" t="s">
@@ -2302,25 +3701,25 @@
         <v>1500</v>
       </c>
       <c r="L23">
+        <f t="shared" si="4"/>
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="11">
+        <v>9000</v>
+      </c>
+      <c r="C24" s="11">
+        <v>9000</v>
+      </c>
+      <c r="D24" s="11">
+        <v>9000</v>
+      </c>
+      <c r="E24" s="12">
         <f t="shared" si="3"/>
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="12">
-        <v>9000</v>
-      </c>
-      <c r="C24" s="12">
-        <v>9000</v>
-      </c>
-      <c r="D24" s="12">
-        <v>9000</v>
-      </c>
-      <c r="E24" s="13">
-        <f t="shared" si="2"/>
         <v>27000</v>
       </c>
       <c r="H24" t="s">
@@ -2336,25 +3735,25 @@
         <v>9000</v>
       </c>
       <c r="L24">
+        <f t="shared" si="4"/>
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="11">
+        <v>3300</v>
+      </c>
+      <c r="C25" s="11">
+        <v>3300</v>
+      </c>
+      <c r="D25" s="11">
+        <v>3300</v>
+      </c>
+      <c r="E25" s="12">
         <f t="shared" si="3"/>
-        <v>27000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="12">
-        <v>3300</v>
-      </c>
-      <c r="C25" s="12">
-        <v>3300</v>
-      </c>
-      <c r="D25" s="12">
-        <v>3300</v>
-      </c>
-      <c r="E25" s="13">
-        <f t="shared" si="2"/>
         <v>9900</v>
       </c>
       <c r="H25" t="s">
@@ -2370,18 +3769,18 @@
         <v>3300</v>
       </c>
       <c r="L25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9900</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="14">
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="13">
         <f>SUM(E16:E25)</f>
         <v>95657</v>
       </c>
@@ -2922,263 +4321,263 @@
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="55.8" thickBot="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" ht="28.2" thickBot="1">
+      <c r="A1" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="14">
         <v>2</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="16">
         <v>46023</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="16">
         <v>46024</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="16">
         <v>46023</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F2" s="16">
         <v>46023</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="14">
         <v>0.99999999999998845</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>2</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>4</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="16">
         <v>46024</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <v>46027</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="16">
         <v>46054</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="16">
         <v>46388</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="14">
         <v>7.1249999999999911</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>8</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <v>46025</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>46028</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="16">
         <v>46082</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="16">
         <v>46753</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="14">
         <v>13.249999999999993</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>16</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>46026</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>46029</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>46113</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="16">
         <v>47119</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="14">
         <v>19.374999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" thickBot="1">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>32</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <v>46027</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <v>46030</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="16">
         <v>46143</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="16">
         <v>47484</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <v>25.5</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" thickBot="1">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>64</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>46028</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>46031</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>46174</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <v>47849</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="14">
         <v>31.625</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" thickBot="1">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>128</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>46029</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>46034</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="16">
         <v>46204</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="16">
         <v>48214</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>37.750000000000007</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" thickBot="1">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>8</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>256</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>46030</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <v>46035</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>46235</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="16">
         <v>48580</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="14">
         <v>43.875000000000007</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" thickBot="1">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>9</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>512</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>46031</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <v>46036</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <v>46266</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <v>48945</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="14">
         <v>50.000000000000007</v>
       </c>
     </row>
@@ -3203,7 +4602,2222 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21A5E7B-937C-4B68-8F8C-6684494D192D}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="19">
+        <f ca="1">TODAY()</f>
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="19">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="19">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="19">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="19">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="19">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="19">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="19">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="19">
+        <v>46202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42EE49C0-9709-480B-B2EB-E6CC416330B0}">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="21">
+        <v>16000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="20">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" s="21">
+        <v>1890</v>
+      </c>
+      <c r="E3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="20">
+        <v>44928</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="21">
+        <v>1650</v>
+      </c>
+      <c r="E4" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="20">
+        <v>44929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="21">
+        <v>1074</v>
+      </c>
+      <c r="E5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="20">
+        <v>44930</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="21">
+        <v>1000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H6" s="20">
+        <v>44931</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7">
+        <v>890</v>
+      </c>
+      <c r="E7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="20">
+        <v>44932</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8">
+        <v>780</v>
+      </c>
+      <c r="E8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="20">
+        <v>44933</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9">
+        <v>530</v>
+      </c>
+      <c r="E9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" s="20">
+        <v>44934</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10">
+        <v>456</v>
+      </c>
+      <c r="E10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H10" s="20">
+        <v>44935</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11">
+        <v>300</v>
+      </c>
+      <c r="E11" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="20">
+        <v>44936</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12">
+        <v>257</v>
+      </c>
+      <c r="E12" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="20">
+        <v>44937</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13">
+        <v>120</v>
+      </c>
+      <c r="E13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H13" s="20">
+        <v>44938</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14">
+        <v>120</v>
+      </c>
+      <c r="E14" t="s">
+        <v>211</v>
+      </c>
+      <c r="H14" s="20">
+        <v>44939</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15" t="s">
+        <v>211</v>
+      </c>
+      <c r="H15" s="20">
+        <v>44940</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="20">
+        <v>44941</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>218</v>
+      </c>
+      <c r="H17" s="20">
+        <v>44942</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H18" s="20">
+        <v>44943</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>211</v>
+      </c>
+      <c r="H19" s="20">
+        <v>44944</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>233</v>
+      </c>
+      <c r="B20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" t="s">
+        <v>235</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" s="20">
+        <v>44945</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H2:H20">
+    <sortCondition descending="1" ref="H10:H20"/>
+  </sortState>
+  <conditionalFormatting sqref="E2:E20">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>10000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>10000</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CEBBED-590C-410D-97B6-30A31DF6C1B4}">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="20">
+        <v>44927</v>
+      </c>
+      <c r="B2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="21">
+        <v>16000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="20">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="20">
+        <v>44928</v>
+      </c>
+      <c r="B3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" s="21">
+        <v>1890</v>
+      </c>
+      <c r="E3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="20">
+        <v>44928</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="20">
+        <v>44929</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="21">
+        <v>1650</v>
+      </c>
+      <c r="E4" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="20">
+        <v>44929</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="20">
+        <v>44930</v>
+      </c>
+      <c r="B5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="21">
+        <v>1074</v>
+      </c>
+      <c r="E5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="20">
+        <v>44930</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="20">
+        <v>44931</v>
+      </c>
+      <c r="B6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="21">
+        <v>1000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H6" s="20">
+        <v>44931</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="20">
+        <v>44932</v>
+      </c>
+      <c r="B7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7">
+        <v>890</v>
+      </c>
+      <c r="E7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="20">
+        <v>44932</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="20">
+        <v>44933</v>
+      </c>
+      <c r="B8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8">
+        <v>780</v>
+      </c>
+      <c r="E8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="20">
+        <v>44933</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="20">
+        <v>44934</v>
+      </c>
+      <c r="B9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9">
+        <v>530</v>
+      </c>
+      <c r="E9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" s="20">
+        <v>44934</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="20">
+        <v>44935</v>
+      </c>
+      <c r="B10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10">
+        <v>456</v>
+      </c>
+      <c r="E10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H10" s="20">
+        <v>44935</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="20">
+        <v>44936</v>
+      </c>
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11">
+        <v>300</v>
+      </c>
+      <c r="E11" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="20">
+        <v>44936</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="20">
+        <v>44937</v>
+      </c>
+      <c r="B12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12">
+        <v>257</v>
+      </c>
+      <c r="E12" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="20">
+        <v>44937</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="20">
+        <v>44938</v>
+      </c>
+      <c r="B13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13">
+        <v>120</v>
+      </c>
+      <c r="E13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H13" s="20">
+        <v>44938</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="20">
+        <v>44939</v>
+      </c>
+      <c r="B14" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14">
+        <v>120</v>
+      </c>
+      <c r="E14" t="s">
+        <v>211</v>
+      </c>
+      <c r="H14" s="20">
+        <v>44939</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="20">
+        <v>44940</v>
+      </c>
+      <c r="B15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15" t="s">
+        <v>211</v>
+      </c>
+      <c r="H15" s="20">
+        <v>44940</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="20">
+        <v>44941</v>
+      </c>
+      <c r="B16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="20">
+        <v>44941</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="20">
+        <v>44942</v>
+      </c>
+      <c r="B17" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>218</v>
+      </c>
+      <c r="H17" s="20">
+        <v>44942</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="20">
+        <v>44943</v>
+      </c>
+      <c r="B18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H18" s="20">
+        <v>44943</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="20">
+        <v>44944</v>
+      </c>
+      <c r="B19" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>211</v>
+      </c>
+      <c r="H19" s="20">
+        <v>44944</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="20">
+        <v>44945</v>
+      </c>
+      <c r="B20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" t="s">
+        <v>235</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" s="20">
+        <v>44945</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E20" xr:uid="{E9CEBBED-590C-410D-97B6-30A31DF6C1B4}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{230B377F-B4E5-4009-9350-25751DC3B630}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" customWidth="1"/>
+    <col min="12" max="12" width="16.21875" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="42" thickBot="1">
+      <c r="A1" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15" thickBot="1">
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45000</v>
+      </c>
+      <c r="D2" s="24">
+        <v>0.18</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2500</v>
+      </c>
+      <c r="F2" s="2">
+        <f>B2*C2</f>
+        <v>225000</v>
+      </c>
+      <c r="G2" s="2">
+        <f>F2-E2</f>
+        <v>222500</v>
+      </c>
+      <c r="H2" s="2">
+        <f>G2/B2</f>
+        <v>44500</v>
+      </c>
+      <c r="J2">
+        <v>150</v>
+      </c>
+      <c r="K2">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>200</v>
+      </c>
+      <c r="M2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="28.2" thickBot="1">
+      <c r="A3" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="2">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>15000</v>
+      </c>
+      <c r="D3" s="24">
+        <v>0.12</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F6" si="0">B3*C3</f>
+        <v>150000</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G6" si="1">F3-E3</f>
+        <v>149000</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H6" si="2">G3/B3</f>
+        <v>14900</v>
+      </c>
+      <c r="J3">
+        <v>200</v>
+      </c>
+      <c r="K3">
+        <v>15</v>
+      </c>
+      <c r="L3">
+        <v>150</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="28.2" thickBot="1">
+      <c r="A4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="2">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2">
+        <v>800</v>
+      </c>
+      <c r="D4" s="24">
+        <v>0.18</v>
+      </c>
+      <c r="E4" s="2">
+        <v>150</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>40000</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="1"/>
+        <v>39850</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="2"/>
+        <v>797</v>
+      </c>
+      <c r="J4">
+        <f>SUM(J2,J3)</f>
+        <v>350</v>
+      </c>
+      <c r="K4">
+        <f>K2*K3</f>
+        <v>300</v>
+      </c>
+      <c r="L4">
+        <f>L2-L3</f>
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <f>M2/M3</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" thickBot="1">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D5" s="24">
+        <v>0.18</v>
+      </c>
+      <c r="E5" s="2">
+        <v>200</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>36000</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="1"/>
+        <v>35800</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
+        <v>1193.3333333333333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" thickBot="1">
+      <c r="A6" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B6" s="2">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
+        <v>11000</v>
+      </c>
+      <c r="D6" s="24">
+        <v>0.18</v>
+      </c>
+      <c r="E6" s="2">
+        <v>800</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>88000</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="1"/>
+        <v>87200</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>10900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956133B7-0AAE-431E-8832-16624288E12E}">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="27.6">
+      <c r="A1" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="27" t="str">
+        <f>CONCATENATE(A2," ",B2," ",C2)</f>
+        <v>MR. JON YANG</v>
+      </c>
+      <c r="E2" s="27" t="str">
+        <f>LOWER(D2)</f>
+        <v>mr. jon yang</v>
+      </c>
+      <c r="F2" s="27" t="str">
+        <f>UPPER(E2)</f>
+        <v>MR. JON YANG</v>
+      </c>
+      <c r="G2" s="27" t="str">
+        <f>PROPER(F2)</f>
+        <v>Mr. Jon Yang</v>
+      </c>
+      <c r="H2" s="27">
+        <f>LEN(D2)</f>
+        <v>12</v>
+      </c>
+      <c r="I2" s="27" t="str">
+        <f>LEFT(B2,2)</f>
+        <v>JO</v>
+      </c>
+      <c r="J2" s="27" t="str">
+        <f>RIGHT(B2,2)</f>
+        <v>ON</v>
+      </c>
+      <c r="K2" t="str">
+        <f>MID(C2,2,3)</f>
+        <v>ANG</v>
+      </c>
+      <c r="L2" t="e">
+        <f>FIND("o",D2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M2">
+        <f>SEARCH("o",D2)</f>
+        <v>6</v>
+      </c>
+      <c r="N2" t="str">
+        <f>REPLACE(B2,2,1,"I")</f>
+        <v>JIN</v>
+      </c>
+      <c r="O2" t="str">
+        <f>SUBSTITUTE(B3,"E","i")</f>
+        <v>iUGiNi</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="27.6">
+      <c r="A3" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="27" t="str">
+        <f t="shared" ref="D3:D20" si="0">CONCATENATE(A3," ",B3," ",C3)</f>
+        <v>MR. EUGENE HUANG</v>
+      </c>
+      <c r="E3" s="27" t="str">
+        <f t="shared" ref="E3:E20" si="1">LOWER(D3)</f>
+        <v>mr. eugene huang</v>
+      </c>
+      <c r="F3" s="27" t="str">
+        <f t="shared" ref="F3:F20" si="2">UPPER(E3)</f>
+        <v>MR. EUGENE HUANG</v>
+      </c>
+      <c r="G3" s="27" t="str">
+        <f t="shared" ref="G3:G20" si="3">PROPER(F3)</f>
+        <v>Mr. Eugene Huang</v>
+      </c>
+      <c r="H3" s="27">
+        <f t="shared" ref="H3:H20" si="4">LEN(D3)</f>
+        <v>16</v>
+      </c>
+      <c r="I3" s="27" t="str">
+        <f t="shared" ref="I3:I20" si="5">LEFT(B3,2)</f>
+        <v>EU</v>
+      </c>
+      <c r="J3" s="27" t="str">
+        <f t="shared" ref="J3:J20" si="6">RIGHT(B3,2)</f>
+        <v>NE</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K20" si="7">MID(C3,2,3)</f>
+        <v>UAN</v>
+      </c>
+      <c r="M3" t="e">
+        <f t="shared" ref="M3:M20" si="8">SEARCH("o",D3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="O3:O20" si="9">SUBSTITUTE(B4,"E","i")</f>
+        <v>RUBiN</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="27.6">
+      <c r="A4" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. RUBEN TORRES</v>
+      </c>
+      <c r="E4" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. ruben torres</v>
+      </c>
+      <c r="F4" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. RUBEN TORRES</v>
+      </c>
+      <c r="G4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Ruben Torres</v>
+      </c>
+      <c r="H4" s="27">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="I4" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>RU</v>
+      </c>
+      <c r="J4" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>EN</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" si="7"/>
+        <v>ORR</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="O4" t="str">
+        <f t="shared" si="9"/>
+        <v>CHRISTY</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="27.6">
+      <c r="A5" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MS. CHRISTY ZHU</v>
+      </c>
+      <c r="E5" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>ms. christy zhu</v>
+      </c>
+      <c r="F5" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MS. CHRISTY ZHU</v>
+      </c>
+      <c r="G5" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Ms. Christy Zhu</v>
+      </c>
+      <c r="H5" s="27">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="I5" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>CH</v>
+      </c>
+      <c r="J5" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>TY</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="7"/>
+        <v>HU</v>
+      </c>
+      <c r="M5" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="9"/>
+        <v>iLIZABiTH</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="41.4">
+      <c r="A6" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MRS. ELIZABETH JOHNSON</v>
+      </c>
+      <c r="E6" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mrs. elizabeth johnson</v>
+      </c>
+      <c r="F6" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MRS. ELIZABETH JOHNSON</v>
+      </c>
+      <c r="G6" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mrs. Elizabeth Johnson</v>
+      </c>
+      <c r="H6" s="27">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="I6" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>EL</v>
+      </c>
+      <c r="J6" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>TH</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="7"/>
+        <v>OHN</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="8"/>
+        <v>17</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="9"/>
+        <v>JULIO</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="27.6">
+      <c r="A7" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. JULIO RUIZ</v>
+      </c>
+      <c r="E7" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. julio ruiz</v>
+      </c>
+      <c r="F7" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. JULIO RUIZ</v>
+      </c>
+      <c r="G7" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Julio Ruiz</v>
+      </c>
+      <c r="H7" s="27">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="I7" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>JU</v>
+      </c>
+      <c r="J7" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>IO</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="7"/>
+        <v>UIZ</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="9"/>
+        <v>MARCO</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="27.6">
+      <c r="A8" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. MARCO MEHTA</v>
+      </c>
+      <c r="E8" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. marco mehta</v>
+      </c>
+      <c r="F8" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. MARCO MEHTA</v>
+      </c>
+      <c r="G8" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Marco Mehta</v>
+      </c>
+      <c r="H8" s="27">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="I8" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>MA</v>
+      </c>
+      <c r="J8" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>CO</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="7"/>
+        <v>EHT</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="9"/>
+        <v>ROBIN</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="27.6">
+      <c r="A9" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MRS. ROBIN VERHOFF</v>
+      </c>
+      <c r="E9" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mrs. robin verhoff</v>
+      </c>
+      <c r="F9" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MRS. ROBIN VERHOFF</v>
+      </c>
+      <c r="G9" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mrs. Robin Verhoff</v>
+      </c>
+      <c r="H9" s="27">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="I9" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>RO</v>
+      </c>
+      <c r="J9" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>IN</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="7"/>
+        <v>ERH</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="9"/>
+        <v>SHANNON</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="27.6">
+      <c r="A10" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. SHANNON CARLSON</v>
+      </c>
+      <c r="E10" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. shannon carlson</v>
+      </c>
+      <c r="F10" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. SHANNON CARLSON</v>
+      </c>
+      <c r="G10" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Shannon Carlson</v>
+      </c>
+      <c r="H10" s="27">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="I10" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>SH</v>
+      </c>
+      <c r="J10" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>ON</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="7"/>
+        <v>ARL</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="9"/>
+        <v>JACQUiLY</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="41.4">
+      <c r="A11" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MS. JACQUELY SUAREZ</v>
+      </c>
+      <c r="E11" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>ms. jacquely suarez</v>
+      </c>
+      <c r="F11" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MS. JACQUELY SUAREZ</v>
+      </c>
+      <c r="G11" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Ms. Jacquely Suarez</v>
+      </c>
+      <c r="H11" s="27">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="I11" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>JA</v>
+      </c>
+      <c r="J11" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>LY</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="7"/>
+        <v>UAR</v>
+      </c>
+      <c r="M11" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="9"/>
+        <v>CURTIS</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="27.6">
+      <c r="A12" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. CURTIS LU</v>
+      </c>
+      <c r="E12" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. curtis lu</v>
+      </c>
+      <c r="F12" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. CURTIS LU</v>
+      </c>
+      <c r="G12" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Curtis Lu</v>
+      </c>
+      <c r="H12" s="27">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="I12" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>CU</v>
+      </c>
+      <c r="J12" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>IS</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="7"/>
+        <v>U</v>
+      </c>
+      <c r="M12" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="9"/>
+        <v>LAURiN</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="27.6">
+      <c r="A13" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MRS. LAUREN WALKER</v>
+      </c>
+      <c r="E13" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mrs. lauren walker</v>
+      </c>
+      <c r="F13" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MRS. LAUREN WALKER</v>
+      </c>
+      <c r="G13" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mrs. Lauren Walker</v>
+      </c>
+      <c r="H13" s="27">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="I13" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>LA</v>
+      </c>
+      <c r="J13" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>EN</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="7"/>
+        <v>ALK</v>
+      </c>
+      <c r="M13" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="9"/>
+        <v>IAN</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="27.6">
+      <c r="A14" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. IAN JENKINS</v>
+      </c>
+      <c r="E14" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. ian jenkins</v>
+      </c>
+      <c r="F14" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. IAN JENKINS</v>
+      </c>
+      <c r="G14" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Ian Jenkins</v>
+      </c>
+      <c r="H14" s="27">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="I14" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>IA</v>
+      </c>
+      <c r="J14" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>AN</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="7"/>
+        <v>ENK</v>
+      </c>
+      <c r="M14" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="9"/>
+        <v>SYDNiY</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="27.6">
+      <c r="A15" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MRS. SYDNEY BENNETT</v>
+      </c>
+      <c r="E15" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mrs. sydney bennett</v>
+      </c>
+      <c r="F15" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MRS. SYDNEY BENNETT</v>
+      </c>
+      <c r="G15" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mrs. Sydney Bennett</v>
+      </c>
+      <c r="H15" s="27">
+        <f t="shared" si="4"/>
+        <v>19</v>
+      </c>
+      <c r="I15" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>SY</v>
+      </c>
+      <c r="J15" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>EY</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="7"/>
+        <v>ENN</v>
+      </c>
+      <c r="M15" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="9"/>
+        <v>CHLOi</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="27.6">
+      <c r="A16" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MS. CHLOE YOUNG</v>
+      </c>
+      <c r="E16" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>ms. chloe young</v>
+      </c>
+      <c r="F16" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MS. CHLOE YOUNG</v>
+      </c>
+      <c r="G16" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Ms. Chloe Young</v>
+      </c>
+      <c r="H16" s="27">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="I16" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>CH</v>
+      </c>
+      <c r="J16" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>OE</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="7"/>
+        <v>OUN</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="9"/>
+        <v>WYATT</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="27.6">
+      <c r="A17" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. WYATT HILL</v>
+      </c>
+      <c r="E17" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. wyatt hill</v>
+      </c>
+      <c r="F17" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. WYATT HILL</v>
+      </c>
+      <c r="G17" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Wyatt Hill</v>
+      </c>
+      <c r="H17" s="27">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="I17" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>WY</v>
+      </c>
+      <c r="J17" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>TT</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="7"/>
+        <v>ILL</v>
+      </c>
+      <c r="M17" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="9"/>
+        <v>SHANNON</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="41.4">
+      <c r="A18" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MRS. SHANNON WANG</v>
+      </c>
+      <c r="E18" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mrs. shannon wang</v>
+      </c>
+      <c r="F18" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MRS. SHANNON WANG</v>
+      </c>
+      <c r="G18" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mrs. Shannon Wang</v>
+      </c>
+      <c r="H18" s="27">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="I18" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>SH</v>
+      </c>
+      <c r="J18" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>ON</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="7"/>
+        <v>ANG</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="9"/>
+        <v>CLARiNCi</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="41.4">
+      <c r="A19" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. CLARENCE RAI</v>
+      </c>
+      <c r="E19" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. clarence rai</v>
+      </c>
+      <c r="F19" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. CLARENCE RAI</v>
+      </c>
+      <c r="G19" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Clarence Rai</v>
+      </c>
+      <c r="H19" s="27">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="I19" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>CL</v>
+      </c>
+      <c r="J19" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>CE</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="7"/>
+        <v>AI</v>
+      </c>
+      <c r="M19" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="9"/>
+        <v>LUKi</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>275</v>
+      </c>
+      <c r="D20" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>MR. LUKE LAI</v>
+      </c>
+      <c r="E20" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>mr. luke lai</v>
+      </c>
+      <c r="F20" s="27" t="str">
+        <f t="shared" si="2"/>
+        <v>MR. LUKE LAI</v>
+      </c>
+      <c r="G20" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>Mr. Luke Lai</v>
+      </c>
+      <c r="H20" s="27">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="I20" s="27" t="str">
+        <f t="shared" si="5"/>
+        <v>LU</v>
+      </c>
+      <c r="J20" s="27" t="str">
+        <f t="shared" si="6"/>
+        <v>KE</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="7"/>
+        <v>AI</v>
+      </c>
+      <c r="M20" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DB8AA6-D9BD-47DD-870B-8E672E0FE850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1CF5FD-B2BF-4628-83A3-7D397FE5890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="10" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
   </bookViews>
@@ -91,8 +91,63 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={CA49B5B2-41FD-4FA8-9478-4F9F7112986C}</author>
+    <author>tc={CAA42FFD-4F2B-46D8-BDE8-5101D21CA8EC}</author>
+    <author>tc={8D70C464-D227-4410-BA12-BBD9EAC38824}</author>
+    <author>tc={EB89E1C3-B0DF-4EE8-B4B5-1D1525D82F7C}</author>
+    <author>tc={D0E4815C-E4D9-43CB-836F-B2ACC391A9BB}</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{CA49B5B2-41FD-4FA8-9478-4F9F7112986C}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ctrl + :
+</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="1" shapeId="0" xr:uid="{CAA42FFD-4F2B-46D8-BDE8-5101D21CA8EC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    It is used to increase the date with the help of month</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="2" shapeId="0" xr:uid="{8D70C464-D227-4410-BA12-BBD9EAC38824}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    It is used to give the last date of month</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="3" shapeId="0" xr:uid="{EB89E1C3-B0DF-4EE8-B4B5-1D1525D82F7C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ctrl + shift + :</t>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="4" shapeId="0" xr:uid="{D0E4815C-E4D9-43CB-836F-B2ACC391A9BB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    In this we’ve to find date of retirement</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="348">
   <si>
     <t>Mohan</t>
   </si>
@@ -1118,6 +1173,24 @@
   </si>
   <si>
     <t>date +3years</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>yearfrac</t>
+  </si>
+  <si>
+    <t>datedif</t>
+  </si>
+  <si>
+    <t>networkdays</t>
+  </si>
+  <si>
+    <t>Edate</t>
+  </si>
+  <si>
+    <t>Eomonth</t>
   </si>
 </sst>
 </file>
@@ -1125,10 +1198,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1196,6 +1269,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1311,58 +1390,44 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1419,7 +1484,7 @@
     <sortCondition ref="H1:H20"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{245ABA7D-7ECE-4568-A31E-1E8B7C978F00}" name="Dates" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{245ABA7D-7ECE-4568-A31E-1E8B7C978F00}" name="Dates" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1737,6 +1802,27 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2026-06-22T06:13:46.47" personId="{1B580FBE-5650-4AF0-8974-B47F26D25219}" id="{CA49B5B2-41FD-4FA8-9478-4F9F7112986C}">
+    <text xml:space="preserve">Ctrl + :
+</text>
+  </threadedComment>
+  <threadedComment ref="Q2" dT="2026-06-22T06:24:28.83" personId="{1B580FBE-5650-4AF0-8974-B47F26D25219}" id="{CAA42FFD-4F2B-46D8-BDE8-5101D21CA8EC}">
+    <text>It is used to increase the date with the help of month</text>
+  </threadedComment>
+  <threadedComment ref="R2" dT="2026-06-22T06:25:42.95" personId="{1B580FBE-5650-4AF0-8974-B47F26D25219}" id="{8D70C464-D227-4410-BA12-BBD9EAC38824}">
+    <text>It is used to give the last date of month</text>
+  </threadedComment>
+  <threadedComment ref="B4" dT="2026-06-22T06:14:54.02" personId="{1B580FBE-5650-4AF0-8974-B47F26D25219}" id="{EB89E1C3-B0DF-4EE8-B4B5-1D1525D82F7C}">
+    <text>Ctrl + shift + :</text>
+  </threadedComment>
+  <threadedComment ref="Q4" dT="2026-06-22T06:27:19.87" personId="{1B580FBE-5650-4AF0-8974-B47F26D25219}" id="{D0E4815C-E4D9-43CB-836F-B2ACC391A9BB}">
+    <text>In this we’ve to find date of retirement</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED6B353-9C0F-445A-AF5B-135B21ABA93D}">
   <dimension ref="A1:R13"/>
@@ -1900,41 +1986,41 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1962,38 +2048,38 @@
     <col min="11" max="11" width="3.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="31" customFormat="1">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:11" s="29" customFormat="1">
+      <c r="A1" s="29" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>281</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="29" t="s">
         <v>290</v>
       </c>
     </row>
@@ -2013,7 +2099,7 @@
       <c r="E2">
         <v>55</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="17">
         <v>42468</v>
       </c>
       <c r="G2" t="s">
@@ -2052,7 +2138,7 @@
       <c r="E3">
         <v>59</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="17">
         <v>35763</v>
       </c>
       <c r="G3" t="s">
@@ -2091,7 +2177,7 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>39016</v>
       </c>
       <c r="G4" t="s">
@@ -2130,7 +2216,7 @@
       <c r="E5">
         <v>26</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>43735</v>
       </c>
       <c r="G5" t="s">
@@ -2169,7 +2255,7 @@
       <c r="E6">
         <v>55</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <v>35023</v>
       </c>
       <c r="G6" t="s">
@@ -2208,7 +2294,7 @@
       <c r="E7">
         <v>57</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <v>42759</v>
       </c>
       <c r="G7" t="s">
@@ -2247,7 +2333,7 @@
       <c r="E8">
         <v>27</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>44013</v>
       </c>
       <c r="G8" t="s">
@@ -2286,7 +2372,7 @@
       <c r="E9">
         <v>25</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>43967</v>
       </c>
       <c r="G9" t="s">
@@ -2325,7 +2411,7 @@
       <c r="E10">
         <v>29</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <v>43490</v>
       </c>
       <c r="G10" t="s">
@@ -2364,7 +2450,7 @@
       <c r="E11">
         <v>34</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>43264</v>
       </c>
       <c r="G11" t="s">
@@ -2403,7 +2489,7 @@
       <c r="E12">
         <v>36</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <v>39855</v>
       </c>
       <c r="G12" t="s">
@@ -2442,7 +2528,7 @@
       <c r="E13">
         <v>27</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <v>44490</v>
       </c>
       <c r="G13" t="s">
@@ -2481,7 +2567,7 @@
       <c r="E14">
         <v>59</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <v>36233</v>
       </c>
       <c r="G14" t="s">
@@ -2520,7 +2606,7 @@
       <c r="E15">
         <v>51</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <v>44357</v>
       </c>
       <c r="G15" t="s">
@@ -2559,7 +2645,7 @@
       <c r="E16">
         <v>31</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="17">
         <v>43043</v>
       </c>
       <c r="G16" t="s">
@@ -2598,7 +2684,7 @@
       <c r="E17">
         <v>41</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>41346</v>
       </c>
       <c r="G17" t="s">
@@ -2637,7 +2723,7 @@
       <c r="E18">
         <v>65</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <v>37319</v>
       </c>
       <c r="G18" t="s">
@@ -2676,7 +2762,7 @@
       <c r="E19">
         <v>64</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <v>37956</v>
       </c>
       <c r="G19" t="s">
@@ -2715,7 +2801,7 @@
       <c r="E20">
         <v>64</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <v>41581</v>
       </c>
       <c r="G20" t="s">
@@ -2744,55 +2830,231 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EC6E42-5F38-4262-90E2-276AAD0D4F4E}">
-  <dimension ref="A1:L1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EC6E42-5F38-4262-90E2-276AAD0D4F4E}">
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>335</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="29" t="s">
         <v>336</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="29" t="s">
         <v>338</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="29" t="s">
         <v>339</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="29" t="s">
         <v>341</v>
+      </c>
+      <c r="M1" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="N1" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="P1" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q1" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="R1" s="29" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="17">
+        <f ca="1">TODAY()</f>
+        <v>46195</v>
+      </c>
+      <c r="B2" s="32">
+        <f ca="1">NOW()</f>
+        <v>46195.497613425927</v>
+      </c>
+      <c r="C2">
+        <f ca="1">DAY(B2)</f>
+        <v>22</v>
+      </c>
+      <c r="D2">
+        <f ca="1">MONTH(B2)</f>
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <f ca="1">YEAR(B2)</f>
+        <v>2026</v>
+      </c>
+      <c r="F2" s="17">
+        <f ca="1">DATE(E2,D2,C2)</f>
+        <v>46195</v>
+      </c>
+      <c r="G2">
+        <f ca="1">HOUR(B2)</f>
+        <v>11</v>
+      </c>
+      <c r="H2">
+        <f ca="1">MINUTE(B2)</f>
+        <v>56</v>
+      </c>
+      <c r="I2">
+        <f ca="1">SECOND(B2)</f>
+        <v>34</v>
+      </c>
+      <c r="J2" s="17">
+        <f ca="1">A2+3</f>
+        <v>46198</v>
+      </c>
+      <c r="K2" s="17">
+        <f ca="1">EDATE(A2,3)</f>
+        <v>46287</v>
+      </c>
+      <c r="L2" s="17">
+        <f ca="1">EDATE(A2,(12*3))</f>
+        <v>47291</v>
+      </c>
+      <c r="M2" t="str">
+        <f ca="1">TEXT(A2,"D")</f>
+        <v>22</v>
+      </c>
+      <c r="N2">
+        <f ca="1">YEARFRAC(A2,L2)</f>
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <f ca="1">DATEDIF(A2,L2,"y")</f>
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <f ca="1">NETWORKDAYS(A2,K2)</f>
+        <v>67</v>
+      </c>
+      <c r="Q2" s="17">
+        <f ca="1">EDATE(A2,11)</f>
+        <v>46529</v>
+      </c>
+      <c r="R2" s="17">
+        <f ca="1">EOMONTH(A2,0)</f>
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="M3" t="str">
+        <f ca="1">TEXT(A2,"DD")</f>
+        <v>22</v>
+      </c>
+      <c r="N3">
+        <f ca="1">YEARFRAC(A2,K2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="P3">
+        <f ca="1">NETWORKDAYS.INTL(A2,L2)</f>
+        <v>785</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="B4" s="33">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="M4" t="str">
+        <f ca="1">TEXT(A2,"DDD")</f>
+        <v>Mon</v>
+      </c>
+      <c r="Q4" s="17">
+        <f ca="1">EDATE(A2,12*60)</f>
+        <v>68110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="M5" t="str">
+        <f ca="1">TEXT(A2,"dddd")</f>
+        <v>Monday</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="M6" t="str">
+        <f ca="1">TEXT(A2,"M")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="M7" t="str">
+        <f ca="1">TEXT(A2,"MM")</f>
+        <v>06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="M8" t="str">
+        <f ca="1">TEXT(A2,"MMM")</f>
+        <v>Jun</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="M9" t="str">
+        <f ca="1">TEXT(A2,"MMMM")</f>
+        <v>June</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="M10" t="str">
+        <f ca="1">TEXT(B2,"Y")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="M11" t="str">
+        <f ca="1">TEXT(B2,"YY")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="M12" t="str">
+        <f ca="1">TEXT(B2,"YYY")</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="M13" t="str">
+        <f ca="1">TEXT(B2,"YYYY")</f>
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4616,48 +4878,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="19">
+      <c r="A1" s="18">
         <f ca="1">TODAY()</f>
         <v>46195</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="19">
+      <c r="A2" s="18">
         <v>46195</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="19">
+      <c r="A3" s="18">
         <v>46196</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="19">
+      <c r="A4" s="18">
         <v>46197</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="19">
+      <c r="A5" s="18">
         <v>46198</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>46199</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="19">
+      <c r="A7" s="18">
         <v>46200</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>46201</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>46202</v>
       </c>
     </row>
@@ -4709,13 +4971,13 @@
       <c r="C2" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="20">
         <v>16000</v>
       </c>
       <c r="E2" t="s">
         <v>211</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="19">
         <v>44927</v>
       </c>
     </row>
@@ -4729,13 +4991,13 @@
       <c r="C3" t="s">
         <v>213</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="20">
         <v>1890</v>
       </c>
       <c r="E3" t="s">
         <v>211</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="19">
         <v>44928</v>
       </c>
     </row>
@@ -4749,13 +5011,13 @@
       <c r="C4" t="s">
         <v>228</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <v>1650</v>
       </c>
       <c r="E4" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="19">
         <v>44929</v>
       </c>
     </row>
@@ -4769,13 +5031,13 @@
       <c r="C5" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <v>1074</v>
       </c>
       <c r="E5" t="s">
         <v>211</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="19">
         <v>44930</v>
       </c>
     </row>
@@ -4789,13 +5051,13 @@
       <c r="C6" t="s">
         <v>213</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>1000</v>
       </c>
       <c r="E6" t="s">
         <v>214</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <v>44931</v>
       </c>
     </row>
@@ -4815,7 +5077,7 @@
       <c r="E7" t="s">
         <v>211</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="19">
         <v>44932</v>
       </c>
     </row>
@@ -4835,7 +5097,7 @@
       <c r="E8" t="s">
         <v>211</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="19">
         <v>44933</v>
       </c>
     </row>
@@ -4855,7 +5117,7 @@
       <c r="E9" t="s">
         <v>218</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="19">
         <v>44934</v>
       </c>
     </row>
@@ -4875,7 +5137,7 @@
       <c r="E10" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="19">
         <v>44935</v>
       </c>
     </row>
@@ -4895,7 +5157,7 @@
       <c r="E11" t="s">
         <v>211</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="19">
         <v>44936</v>
       </c>
     </row>
@@ -4915,7 +5177,7 @@
       <c r="E12" t="s">
         <v>211</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="19">
         <v>44937</v>
       </c>
     </row>
@@ -4935,7 +5197,7 @@
       <c r="E13" t="s">
         <v>211</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="19">
         <v>44938</v>
       </c>
     </row>
@@ -4955,7 +5217,7 @@
       <c r="E14" t="s">
         <v>211</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="19">
         <v>44939</v>
       </c>
     </row>
@@ -4975,7 +5237,7 @@
       <c r="E15" t="s">
         <v>211</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="19">
         <v>44940</v>
       </c>
     </row>
@@ -4995,7 +5257,7 @@
       <c r="E16" t="s">
         <v>218</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="19">
         <v>44941</v>
       </c>
     </row>
@@ -5015,7 +5277,7 @@
       <c r="E17" t="s">
         <v>218</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="19">
         <v>44942</v>
       </c>
     </row>
@@ -5035,7 +5297,7 @@
       <c r="E18" t="s">
         <v>218</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="19">
         <v>44943</v>
       </c>
     </row>
@@ -5055,7 +5317,7 @@
       <c r="E19" t="s">
         <v>211</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="19">
         <v>44944</v>
       </c>
     </row>
@@ -5075,7 +5337,7 @@
       <c r="E20" t="s">
         <v>211</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="19">
         <v>44945</v>
       </c>
     </row>
@@ -5084,12 +5346,6 @@
     <sortCondition descending="1" ref="H10:H20"/>
   </sortState>
   <conditionalFormatting sqref="E2:E20">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
-      <formula>10000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>10000</formula>
-    </cfRule>
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5097,6 +5353,9 @@
         <color rgb="FFFF7128"/>
         <color rgb="FFFFEF9C"/>
       </colorScale>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5120,7 +5379,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>202</v>
       </c>
       <c r="B1" t="s">
@@ -5140,7 +5399,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="20">
+      <c r="A2" s="19">
         <v>44927</v>
       </c>
       <c r="B2" t="s">
@@ -5149,18 +5408,18 @@
       <c r="C2" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="20">
         <v>16000</v>
       </c>
       <c r="E2" t="s">
         <v>211</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="19">
         <v>44927</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="20">
+      <c r="A3" s="19">
         <v>44928</v>
       </c>
       <c r="B3" t="s">
@@ -5169,18 +5428,18 @@
       <c r="C3" t="s">
         <v>213</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="20">
         <v>1890</v>
       </c>
       <c r="E3" t="s">
         <v>211</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="19">
         <v>44928</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="20">
+      <c r="A4" s="19">
         <v>44929</v>
       </c>
       <c r="B4" t="s">
@@ -5189,18 +5448,18 @@
       <c r="C4" t="s">
         <v>228</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <v>1650</v>
       </c>
       <c r="E4" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="19">
         <v>44929</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="20">
+      <c r="A5" s="19">
         <v>44930</v>
       </c>
       <c r="B5" t="s">
@@ -5209,18 +5468,18 @@
       <c r="C5" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <v>1074</v>
       </c>
       <c r="E5" t="s">
         <v>211</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="19">
         <v>44930</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>44931</v>
       </c>
       <c r="B6" t="s">
@@ -5229,18 +5488,18 @@
       <c r="C6" t="s">
         <v>213</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>1000</v>
       </c>
       <c r="E6" t="s">
         <v>214</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <v>44931</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="20">
+      <c r="A7" s="19">
         <v>44932</v>
       </c>
       <c r="B7" t="s">
@@ -5255,12 +5514,12 @@
       <c r="E7" t="s">
         <v>211</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="19">
         <v>44932</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="20">
+      <c r="A8" s="19">
         <v>44933</v>
       </c>
       <c r="B8" t="s">
@@ -5275,12 +5534,12 @@
       <c r="E8" t="s">
         <v>211</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="19">
         <v>44933</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="20">
+      <c r="A9" s="19">
         <v>44934</v>
       </c>
       <c r="B9" t="s">
@@ -5295,12 +5554,12 @@
       <c r="E9" t="s">
         <v>218</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="19">
         <v>44934</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>44935</v>
       </c>
       <c r="B10" t="s">
@@ -5315,12 +5574,12 @@
       <c r="E10" t="s">
         <v>218</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="19">
         <v>44935</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="20">
+      <c r="A11" s="19">
         <v>44936</v>
       </c>
       <c r="B11" t="s">
@@ -5335,12 +5594,12 @@
       <c r="E11" t="s">
         <v>211</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="19">
         <v>44936</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="20">
+      <c r="A12" s="19">
         <v>44937</v>
       </c>
       <c r="B12" t="s">
@@ -5355,12 +5614,12 @@
       <c r="E12" t="s">
         <v>211</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="19">
         <v>44937</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="20">
+      <c r="A13" s="19">
         <v>44938</v>
       </c>
       <c r="B13" t="s">
@@ -5375,12 +5634,12 @@
       <c r="E13" t="s">
         <v>211</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="19">
         <v>44938</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="20">
+      <c r="A14" s="19">
         <v>44939</v>
       </c>
       <c r="B14" t="s">
@@ -5395,12 +5654,12 @@
       <c r="E14" t="s">
         <v>211</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="19">
         <v>44939</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="20">
+      <c r="A15" s="19">
         <v>44940</v>
       </c>
       <c r="B15" t="s">
@@ -5415,12 +5674,12 @@
       <c r="E15" t="s">
         <v>211</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="19">
         <v>44940</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <v>44941</v>
       </c>
       <c r="B16" t="s">
@@ -5435,12 +5694,12 @@
       <c r="E16" t="s">
         <v>218</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="19">
         <v>44941</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="20">
+      <c r="A17" s="19">
         <v>44942</v>
       </c>
       <c r="B17" t="s">
@@ -5455,12 +5714,12 @@
       <c r="E17" t="s">
         <v>218</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="19">
         <v>44942</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="20">
+      <c r="A18" s="19">
         <v>44943</v>
       </c>
       <c r="B18" t="s">
@@ -5475,12 +5734,12 @@
       <c r="E18" t="s">
         <v>218</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="19">
         <v>44943</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="20">
+      <c r="A19" s="19">
         <v>44944</v>
       </c>
       <c r="B19" t="s">
@@ -5495,12 +5754,12 @@
       <c r="E19" t="s">
         <v>211</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="19">
         <v>44944</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="20">
+      <c r="A20" s="19">
         <v>44945</v>
       </c>
       <c r="B20" t="s">
@@ -5515,7 +5774,7 @@
       <c r="E20" t="s">
         <v>211</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="19">
         <v>44945</v>
       </c>
     </row>
@@ -5545,40 +5804,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="42" thickBot="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>258</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="24" t="s">
         <v>259</v>
       </c>
     </row>
@@ -5592,7 +5851,7 @@
       <c r="C2" s="2">
         <v>45000</v>
       </c>
-      <c r="D2" s="24">
+      <c r="D2" s="23">
         <v>0.18</v>
       </c>
       <c r="E2" s="2">
@@ -5633,7 +5892,7 @@
       <c r="C3" s="2">
         <v>15000</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="23">
         <v>0.12</v>
       </c>
       <c r="E3" s="2">
@@ -5674,7 +5933,7 @@
       <c r="C4" s="2">
         <v>800</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <v>0.18</v>
       </c>
       <c r="E4" s="2">
@@ -5719,7 +5978,7 @@
       <c r="C5" s="2">
         <v>1200</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="23">
         <v>0.18</v>
       </c>
       <c r="E5" s="2">
@@ -5748,7 +6007,7 @@
       <c r="C6" s="2">
         <v>11000</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>0.18</v>
       </c>
       <c r="E6" s="2">
@@ -5794,87 +6053,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.6">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="25" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="27" t="str">
+      <c r="D2" s="11" t="str">
         <f>CONCATENATE(A2," ",B2," ",C2)</f>
         <v>MR. JON YANG</v>
       </c>
-      <c r="E2" s="27" t="str">
+      <c r="E2" s="11" t="str">
         <f>LOWER(D2)</f>
         <v>mr. jon yang</v>
       </c>
-      <c r="F2" s="27" t="str">
+      <c r="F2" s="11" t="str">
         <f>UPPER(E2)</f>
         <v>MR. JON YANG</v>
       </c>
-      <c r="G2" s="27" t="str">
+      <c r="G2" s="11" t="str">
         <f>PROPER(F2)</f>
         <v>Mr. Jon Yang</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="11">
         <f>LEN(D2)</f>
         <v>12</v>
       </c>
-      <c r="I2" s="27" t="str">
+      <c r="I2" s="11" t="str">
         <f>LEFT(B2,2)</f>
         <v>JO</v>
       </c>
-      <c r="J2" s="27" t="str">
+      <c r="J2" s="11" t="str">
         <f>RIGHT(B2,2)</f>
         <v>ON</v>
       </c>
@@ -5900,40 +6159,40 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="27.6">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="27" t="str">
+      <c r="D3" s="11" t="str">
         <f t="shared" ref="D3:D20" si="0">CONCATENATE(A3," ",B3," ",C3)</f>
         <v>MR. EUGENE HUANG</v>
       </c>
-      <c r="E3" s="27" t="str">
+      <c r="E3" s="11" t="str">
         <f t="shared" ref="E3:E20" si="1">LOWER(D3)</f>
         <v>mr. eugene huang</v>
       </c>
-      <c r="F3" s="27" t="str">
+      <c r="F3" s="11" t="str">
         <f t="shared" ref="F3:F20" si="2">UPPER(E3)</f>
         <v>MR. EUGENE HUANG</v>
       </c>
-      <c r="G3" s="27" t="str">
+      <c r="G3" s="11" t="str">
         <f t="shared" ref="G3:G20" si="3">PROPER(F3)</f>
         <v>Mr. Eugene Huang</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="11">
         <f t="shared" ref="H3:H20" si="4">LEN(D3)</f>
         <v>16</v>
       </c>
-      <c r="I3" s="27" t="str">
+      <c r="I3" s="11" t="str">
         <f t="shared" ref="I3:I20" si="5">LEFT(B3,2)</f>
         <v>EU</v>
       </c>
-      <c r="J3" s="27" t="str">
+      <c r="J3" s="11" t="str">
         <f t="shared" ref="J3:J20" si="6">RIGHT(B3,2)</f>
         <v>NE</v>
       </c>
@@ -5951,40 +6210,40 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="27.6">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. RUBEN TORRES</v>
       </c>
-      <c r="E4" s="27" t="str">
+      <c r="E4" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. ruben torres</v>
       </c>
-      <c r="F4" s="27" t="str">
+      <c r="F4" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. RUBEN TORRES</v>
       </c>
-      <c r="G4" s="27" t="str">
+      <c r="G4" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Ruben Torres</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="11">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="I4" s="27" t="str">
+      <c r="I4" s="11" t="str">
         <f t="shared" si="5"/>
         <v>RU</v>
       </c>
-      <c r="J4" s="27" t="str">
+      <c r="J4" s="11" t="str">
         <f t="shared" si="6"/>
         <v>EN</v>
       </c>
@@ -6002,40 +6261,40 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="27.6">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="27" t="str">
+      <c r="D5" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MS. CHRISTY ZHU</v>
       </c>
-      <c r="E5" s="27" t="str">
+      <c r="E5" s="11" t="str">
         <f t="shared" si="1"/>
         <v>ms. christy zhu</v>
       </c>
-      <c r="F5" s="27" t="str">
+      <c r="F5" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MS. CHRISTY ZHU</v>
       </c>
-      <c r="G5" s="27" t="str">
+      <c r="G5" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Ms. Christy Zhu</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="11">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="I5" s="27" t="str">
+      <c r="I5" s="11" t="str">
         <f t="shared" si="5"/>
         <v>CH</v>
       </c>
-      <c r="J5" s="27" t="str">
+      <c r="J5" s="11" t="str">
         <f t="shared" si="6"/>
         <v>TY</v>
       </c>
@@ -6053,7 +6312,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="41.4">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="26" t="s">
         <v>273</v>
       </c>
       <c r="B6" t="s">
@@ -6062,31 +6321,31 @@
       <c r="C6" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="27" t="str">
+      <c r="D6" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MRS. ELIZABETH JOHNSON</v>
       </c>
-      <c r="E6" s="27" t="str">
+      <c r="E6" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mrs. elizabeth johnson</v>
       </c>
-      <c r="F6" s="27" t="str">
+      <c r="F6" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MRS. ELIZABETH JOHNSON</v>
       </c>
-      <c r="G6" s="27" t="str">
+      <c r="G6" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mrs. Elizabeth Johnson</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="11">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="I6" s="27" t="str">
+      <c r="I6" s="11" t="str">
         <f t="shared" si="5"/>
         <v>EL</v>
       </c>
-      <c r="J6" s="27" t="str">
+      <c r="J6" s="11" t="str">
         <f t="shared" si="6"/>
         <v>TH</v>
       </c>
@@ -6104,7 +6363,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="27.6">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="26" t="s">
         <v>270</v>
       </c>
       <c r="B7" t="s">
@@ -6113,31 +6372,31 @@
       <c r="C7" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="27" t="str">
+      <c r="D7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. JULIO RUIZ</v>
       </c>
-      <c r="E7" s="27" t="str">
+      <c r="E7" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. julio ruiz</v>
       </c>
-      <c r="F7" s="27" t="str">
+      <c r="F7" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. JULIO RUIZ</v>
       </c>
-      <c r="G7" s="27" t="str">
+      <c r="G7" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Julio Ruiz</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="11">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="I7" s="27" t="str">
+      <c r="I7" s="11" t="str">
         <f t="shared" si="5"/>
         <v>JU</v>
       </c>
-      <c r="J7" s="27" t="str">
+      <c r="J7" s="11" t="str">
         <f t="shared" si="6"/>
         <v>IO</v>
       </c>
@@ -6155,7 +6414,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="27.6">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="26" t="s">
         <v>270</v>
       </c>
       <c r="B8" t="s">
@@ -6164,31 +6423,31 @@
       <c r="C8" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="27" t="str">
+      <c r="D8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. MARCO MEHTA</v>
       </c>
-      <c r="E8" s="27" t="str">
+      <c r="E8" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. marco mehta</v>
       </c>
-      <c r="F8" s="27" t="str">
+      <c r="F8" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. MARCO MEHTA</v>
       </c>
-      <c r="G8" s="27" t="str">
+      <c r="G8" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Marco Mehta</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="11">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="I8" s="27" t="str">
+      <c r="I8" s="11" t="str">
         <f t="shared" si="5"/>
         <v>MA</v>
       </c>
-      <c r="J8" s="27" t="str">
+      <c r="J8" s="11" t="str">
         <f t="shared" si="6"/>
         <v>CO</v>
       </c>
@@ -6206,7 +6465,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="27.6">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="26" t="s">
         <v>273</v>
       </c>
       <c r="B9" t="s">
@@ -6215,31 +6474,31 @@
       <c r="C9" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="27" t="str">
+      <c r="D9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MRS. ROBIN VERHOFF</v>
       </c>
-      <c r="E9" s="27" t="str">
+      <c r="E9" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mrs. robin verhoff</v>
       </c>
-      <c r="F9" s="27" t="str">
+      <c r="F9" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MRS. ROBIN VERHOFF</v>
       </c>
-      <c r="G9" s="27" t="str">
+      <c r="G9" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mrs. Robin Verhoff</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="11">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="I9" s="27" t="str">
+      <c r="I9" s="11" t="str">
         <f t="shared" si="5"/>
         <v>RO</v>
       </c>
-      <c r="J9" s="27" t="str">
+      <c r="J9" s="11" t="str">
         <f t="shared" si="6"/>
         <v>IN</v>
       </c>
@@ -6257,7 +6516,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="27.6">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="26" t="s">
         <v>270</v>
       </c>
       <c r="B10" t="s">
@@ -6266,31 +6525,31 @@
       <c r="C10" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="27" t="str">
+      <c r="D10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. SHANNON CARLSON</v>
       </c>
-      <c r="E10" s="27" t="str">
+      <c r="E10" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. shannon carlson</v>
       </c>
-      <c r="F10" s="27" t="str">
+      <c r="F10" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. SHANNON CARLSON</v>
       </c>
-      <c r="G10" s="27" t="str">
+      <c r="G10" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Shannon Carlson</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="11">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="I10" s="27" t="str">
+      <c r="I10" s="11" t="str">
         <f t="shared" si="5"/>
         <v>SH</v>
       </c>
-      <c r="J10" s="27" t="str">
+      <c r="J10" s="11" t="str">
         <f t="shared" si="6"/>
         <v>ON</v>
       </c>
@@ -6308,7 +6567,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="41.4">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="26" t="s">
         <v>271</v>
       </c>
       <c r="B11" t="s">
@@ -6317,31 +6576,31 @@
       <c r="C11" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="27" t="str">
+      <c r="D11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MS. JACQUELY SUAREZ</v>
       </c>
-      <c r="E11" s="27" t="str">
+      <c r="E11" s="11" t="str">
         <f t="shared" si="1"/>
         <v>ms. jacquely suarez</v>
       </c>
-      <c r="F11" s="27" t="str">
+      <c r="F11" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MS. JACQUELY SUAREZ</v>
       </c>
-      <c r="G11" s="27" t="str">
+      <c r="G11" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Ms. Jacquely Suarez</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="11">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="I11" s="27" t="str">
+      <c r="I11" s="11" t="str">
         <f t="shared" si="5"/>
         <v>JA</v>
       </c>
-      <c r="J11" s="27" t="str">
+      <c r="J11" s="11" t="str">
         <f t="shared" si="6"/>
         <v>LY</v>
       </c>
@@ -6359,7 +6618,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="27.6">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="26" t="s">
         <v>270</v>
       </c>
       <c r="B12" t="s">
@@ -6368,31 +6627,31 @@
       <c r="C12" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="27" t="str">
+      <c r="D12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. CURTIS LU</v>
       </c>
-      <c r="E12" s="27" t="str">
+      <c r="E12" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. curtis lu</v>
       </c>
-      <c r="F12" s="27" t="str">
+      <c r="F12" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. CURTIS LU</v>
       </c>
-      <c r="G12" s="27" t="str">
+      <c r="G12" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Curtis Lu</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="11">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="I12" s="27" t="str">
+      <c r="I12" s="11" t="str">
         <f t="shared" si="5"/>
         <v>CU</v>
       </c>
-      <c r="J12" s="27" t="str">
+      <c r="J12" s="11" t="str">
         <f t="shared" si="6"/>
         <v>IS</v>
       </c>
@@ -6410,7 +6669,7 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="27.6">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="26" t="s">
         <v>273</v>
       </c>
       <c r="B13" t="s">
@@ -6419,31 +6678,31 @@
       <c r="C13" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="27" t="str">
+      <c r="D13" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MRS. LAUREN WALKER</v>
       </c>
-      <c r="E13" s="27" t="str">
+      <c r="E13" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mrs. lauren walker</v>
       </c>
-      <c r="F13" s="27" t="str">
+      <c r="F13" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MRS. LAUREN WALKER</v>
       </c>
-      <c r="G13" s="27" t="str">
+      <c r="G13" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mrs. Lauren Walker</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="11">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="I13" s="27" t="str">
+      <c r="I13" s="11" t="str">
         <f t="shared" si="5"/>
         <v>LA</v>
       </c>
-      <c r="J13" s="27" t="str">
+      <c r="J13" s="11" t="str">
         <f t="shared" si="6"/>
         <v>EN</v>
       </c>
@@ -6461,7 +6720,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="27.6">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="26" t="s">
         <v>270</v>
       </c>
       <c r="B14" t="s">
@@ -6470,31 +6729,31 @@
       <c r="C14" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="27" t="str">
+      <c r="D14" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. IAN JENKINS</v>
       </c>
-      <c r="E14" s="27" t="str">
+      <c r="E14" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. ian jenkins</v>
       </c>
-      <c r="F14" s="27" t="str">
+      <c r="F14" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. IAN JENKINS</v>
       </c>
-      <c r="G14" s="27" t="str">
+      <c r="G14" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Ian Jenkins</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="11">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="I14" s="27" t="str">
+      <c r="I14" s="11" t="str">
         <f t="shared" si="5"/>
         <v>IA</v>
       </c>
-      <c r="J14" s="27" t="str">
+      <c r="J14" s="11" t="str">
         <f t="shared" si="6"/>
         <v>AN</v>
       </c>
@@ -6512,7 +6771,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="27.6">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="26" t="s">
         <v>273</v>
       </c>
       <c r="B15" t="s">
@@ -6521,31 +6780,31 @@
       <c r="C15" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="27" t="str">
+      <c r="D15" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MRS. SYDNEY BENNETT</v>
       </c>
-      <c r="E15" s="27" t="str">
+      <c r="E15" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mrs. sydney bennett</v>
       </c>
-      <c r="F15" s="27" t="str">
+      <c r="F15" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MRS. SYDNEY BENNETT</v>
       </c>
-      <c r="G15" s="27" t="str">
+      <c r="G15" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mrs. Sydney Bennett</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="11">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="I15" s="27" t="str">
+      <c r="I15" s="11" t="str">
         <f t="shared" si="5"/>
         <v>SY</v>
       </c>
-      <c r="J15" s="27" t="str">
+      <c r="J15" s="11" t="str">
         <f t="shared" si="6"/>
         <v>EY</v>
       </c>
@@ -6563,7 +6822,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="27.6">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="26" t="s">
         <v>271</v>
       </c>
       <c r="B16" t="s">
@@ -6572,31 +6831,31 @@
       <c r="C16" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="27" t="str">
+      <c r="D16" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MS. CHLOE YOUNG</v>
       </c>
-      <c r="E16" s="27" t="str">
+      <c r="E16" s="11" t="str">
         <f t="shared" si="1"/>
         <v>ms. chloe young</v>
       </c>
-      <c r="F16" s="27" t="str">
+      <c r="F16" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MS. CHLOE YOUNG</v>
       </c>
-      <c r="G16" s="27" t="str">
+      <c r="G16" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Ms. Chloe Young</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="11">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="I16" s="27" t="str">
+      <c r="I16" s="11" t="str">
         <f t="shared" si="5"/>
         <v>CH</v>
       </c>
-      <c r="J16" s="27" t="str">
+      <c r="J16" s="11" t="str">
         <f t="shared" si="6"/>
         <v>OE</v>
       </c>
@@ -6614,7 +6873,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="27.6">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="26" t="s">
         <v>270</v>
       </c>
       <c r="B17" t="s">
@@ -6623,31 +6882,31 @@
       <c r="C17" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="27" t="str">
+      <c r="D17" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. WYATT HILL</v>
       </c>
-      <c r="E17" s="27" t="str">
+      <c r="E17" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. wyatt hill</v>
       </c>
-      <c r="F17" s="27" t="str">
+      <c r="F17" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. WYATT HILL</v>
       </c>
-      <c r="G17" s="27" t="str">
+      <c r="G17" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Wyatt Hill</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="11">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="I17" s="27" t="str">
+      <c r="I17" s="11" t="str">
         <f t="shared" si="5"/>
         <v>WY</v>
       </c>
-      <c r="J17" s="27" t="str">
+      <c r="J17" s="11" t="str">
         <f t="shared" si="6"/>
         <v>TT</v>
       </c>
@@ -6665,7 +6924,7 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="41.4">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="26" t="s">
         <v>273</v>
       </c>
       <c r="B18" t="s">
@@ -6674,31 +6933,31 @@
       <c r="C18" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="27" t="str">
+      <c r="D18" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MRS. SHANNON WANG</v>
       </c>
-      <c r="E18" s="27" t="str">
+      <c r="E18" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mrs. shannon wang</v>
       </c>
-      <c r="F18" s="27" t="str">
+      <c r="F18" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MRS. SHANNON WANG</v>
       </c>
-      <c r="G18" s="27" t="str">
+      <c r="G18" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mrs. Shannon Wang</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="11">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="I18" s="27" t="str">
+      <c r="I18" s="11" t="str">
         <f t="shared" si="5"/>
         <v>SH</v>
       </c>
-      <c r="J18" s="27" t="str">
+      <c r="J18" s="11" t="str">
         <f t="shared" si="6"/>
         <v>ON</v>
       </c>
@@ -6716,7 +6975,7 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="41.4">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="26" t="s">
         <v>270</v>
       </c>
       <c r="B19" t="s">
@@ -6725,31 +6984,31 @@
       <c r="C19" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="27" t="str">
+      <c r="D19" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. CLARENCE RAI</v>
       </c>
-      <c r="E19" s="27" t="str">
+      <c r="E19" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. clarence rai</v>
       </c>
-      <c r="F19" s="27" t="str">
+      <c r="F19" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. CLARENCE RAI</v>
       </c>
-      <c r="G19" s="27" t="str">
+      <c r="G19" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Clarence Rai</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="11">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="I19" s="27" t="str">
+      <c r="I19" s="11" t="str">
         <f t="shared" si="5"/>
         <v>CL</v>
       </c>
-      <c r="J19" s="27" t="str">
+      <c r="J19" s="11" t="str">
         <f t="shared" si="6"/>
         <v>CE</v>
       </c>
@@ -6767,7 +7026,7 @@
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="26" t="s">
         <v>270</v>
       </c>
       <c r="B20" t="s">
@@ -6776,31 +7035,31 @@
       <c r="C20" t="s">
         <v>275</v>
       </c>
-      <c r="D20" s="27" t="str">
+      <c r="D20" s="11" t="str">
         <f t="shared" si="0"/>
         <v>MR. LUKE LAI</v>
       </c>
-      <c r="E20" s="27" t="str">
+      <c r="E20" s="11" t="str">
         <f t="shared" si="1"/>
         <v>mr. luke lai</v>
       </c>
-      <c r="F20" s="27" t="str">
+      <c r="F20" s="11" t="str">
         <f t="shared" si="2"/>
         <v>MR. LUKE LAI</v>
       </c>
-      <c r="G20" s="27" t="str">
+      <c r="G20" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Mr. Luke Lai</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="11">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="I20" s="27" t="str">
+      <c r="I20" s="11" t="str">
         <f t="shared" si="5"/>
         <v>LU</v>
       </c>
-      <c r="J20" s="27" t="str">
+      <c r="J20" s="11" t="str">
         <f t="shared" si="6"/>
         <v>KE</v>
       </c>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1CF5FD-B2BF-4628-83A3-7D397FE5890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0ACB561-5697-48DE-B891-A3B6433BA6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="10" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="11" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash Fill" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Text Functions" sheetId="10" r:id="rId9"/>
     <sheet name="Logical Functions" sheetId="11" r:id="rId10"/>
     <sheet name="Date and Time Func" sheetId="12" r:id="rId11"/>
+    <sheet name="Sum and Count" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Filteering!$A$1:$E$20</definedName>
@@ -147,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="354">
   <si>
     <t>Mohan</t>
   </si>
@@ -1191,6 +1192,24 @@
   </si>
   <si>
     <t>Eomonth</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>sumif</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>countif</t>
+  </si>
+  <si>
+    <t>sumifs</t>
+  </si>
+  <si>
+    <t>countifs</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1310,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1338,11 +1357,118 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1423,11 +1549,291 @@
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1484,9 +1890,23 @@
     <sortCondition ref="H1:H20"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{245ABA7D-7ECE-4568-A31E-1E8B7C978F00}" name="Dates" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{245ABA7D-7ECE-4568-A31E-1E8B7C978F00}" name="Dates" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4F389F6-B9F3-44FE-A159-BC017026A4C9}" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:E22" xr:uid="{A4F389F6-B9F3-44FE-A159-BC017026A4C9}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{2A627C08-6C83-4E75-BCE6-1A6541F24982}" name="Date" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{E5035FA8-A98E-4E65-ACF0-DBE31FB290DB}" name="Category" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{831F6925-8AC2-4000-82BE-AAB751BED13C}" name="Sub-Category" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{693B7B40-96C4-4EA0-A9E3-23714B1370F2}" name="Amount" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{2387A324-DD9A-48CD-A65C-D45020B4CDE4}" name="Payment Mode" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2904,7 +3324,7 @@
       </c>
       <c r="B2" s="32">
         <f ca="1">NOW()</f>
-        <v>46195.497613425927</v>
+        <v>46195.516931134262</v>
       </c>
       <c r="C2">
         <f ca="1">DAY(B2)</f>
@@ -2924,15 +3344,15 @@
       </c>
       <c r="G2">
         <f ca="1">HOUR(B2)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <f ca="1">MINUTE(B2)</f>
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="I2">
         <f ca="1">SECOND(B2)</f>
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="J2" s="17">
         <f ca="1">A2+3</f>
@@ -3055,6 +3475,455 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDB110B-7A71-4687-9EB2-87F17ADBFFD0}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="28.2" thickBot="1">
+      <c r="A1" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="H1" s="34" t="s">
+        <v>350</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="K1" s="34" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="28.2" thickBot="1">
+      <c r="A2" s="35">
+        <v>44935</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="2">
+        <v>456</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="F2">
+        <f>SUM(D2:D22)</f>
+        <v>25364</v>
+      </c>
+      <c r="G2">
+        <f>SUMIF(Table1[Payment Mode],"UPI",Table1[Amount])</f>
+        <v>23242</v>
+      </c>
+      <c r="H2">
+        <f>COUNT(Table1[Amount])</f>
+        <v>21</v>
+      </c>
+      <c r="I2">
+        <f>COUNTIF(Table1[Payment Mode],"Cash")</f>
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <f>SUMIFS(Table1[Amount],Table1[Payment Mode],"Cash",Table1[Category],"Food")</f>
+        <v>530</v>
+      </c>
+      <c r="K2">
+        <f>COUNTIFS(Table1[Payment Mode],"Cash",Table1[Category],"Food")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15" thickBot="1">
+      <c r="A3" s="35">
+        <v>44945</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="2">
+        <v>26</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1">
+      <c r="A4" s="35">
+        <v>44928</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2">
+        <v>890</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4">
+        <f>SUM(D:D)</f>
+        <v>25364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="28.2" thickBot="1">
+      <c r="A5" s="35">
+        <v>44950</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="2">
+        <v>530</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1">
+      <c r="A6" s="36">
+        <v>44953</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D6" s="2">
+        <v>300</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1">
+      <c r="A7" s="35">
+        <v>44930</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="2">
+        <v>257</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7">
+        <f>SUM(Table1[Amount])</f>
+        <v>25364</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15" thickBot="1">
+      <c r="A8" s="35">
+        <v>44943</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="2">
+        <v>100</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15" thickBot="1">
+      <c r="A9" s="35">
+        <v>44949</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="2">
+        <v>56</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9">
+        <f>SUM(Table1[Amount])</f>
+        <v>25364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1">
+      <c r="A10" s="35">
+        <v>44927</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="2">
+        <v>30</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" thickBot="1">
+      <c r="A11" s="35">
+        <v>44952</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15" thickBot="1">
+      <c r="A12" s="35">
+        <v>44946</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="2">
+        <v>780</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15" thickBot="1">
+      <c r="A13" s="35">
+        <v>44944</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" s="2">
+        <v>120</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" thickBot="1">
+      <c r="A14" s="35">
+        <v>44932</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" s="2">
+        <v>120</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1">
+      <c r="A15" s="35">
+        <v>44941</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="2">
+        <v>50</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15" thickBot="1">
+      <c r="A16" s="35">
+        <v>44948</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1890</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" thickBot="1">
+      <c r="A17" s="35">
+        <v>44947</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1">
+      <c r="A18" s="35">
+        <v>44936</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D18" s="2">
+        <v>16000</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" thickBot="1">
+      <c r="A19" s="35">
+        <v>44955</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1650</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" thickBot="1">
+      <c r="A20" s="35">
+        <v>44956</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1074</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" thickBot="1">
+      <c r="A21" s="35">
+        <v>44953</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="2">
+        <v>10</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="41">
+        <v>44938</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="D22" s="42">
+        <v>15</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5354,7 +6223,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0ACB561-5697-48DE-B891-A3B6433BA6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B826AE99-B430-41F9-A794-0F8799894DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="11" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="10" activeTab="15" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash Fill" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,10 @@
     <sheet name="Logical Functions" sheetId="11" r:id="rId10"/>
     <sheet name="Date and Time Func" sheetId="12" r:id="rId11"/>
     <sheet name="Sum and Count" sheetId="13" r:id="rId12"/>
+    <sheet name="Data Validation" sheetId="14" r:id="rId13"/>
+    <sheet name="Vlookup" sheetId="15" r:id="rId14"/>
+    <sheet name="Hlookup" sheetId="17" r:id="rId15"/>
+    <sheet name="Lookup" sheetId="18" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Filteering!$A$1:$E$20</definedName>
@@ -148,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="430">
   <si>
     <t>Mohan</t>
   </si>
@@ -1210,15 +1214,246 @@
   </si>
   <si>
     <t>countifs</t>
+  </si>
+  <si>
+    <t>Date2</t>
+  </si>
+  <si>
+    <t>Sub-Category2</t>
+  </si>
+  <si>
+    <t>fruits</t>
+  </si>
+  <si>
+    <t>EEID</t>
+  </si>
+  <si>
+    <t>Business Unit</t>
+  </si>
+  <si>
+    <t>Ethnicity</t>
+  </si>
+  <si>
+    <t>Annual Salary</t>
+  </si>
+  <si>
+    <t>Bonus %</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Exit Date</t>
+  </si>
+  <si>
+    <t>E02387</t>
+  </si>
+  <si>
+    <t>Research &amp; Development</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>08-04-2016</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>10/16/2021</t>
+  </si>
+  <si>
+    <t>E04105</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Asian</t>
+  </si>
+  <si>
+    <t>29-11-1997</t>
+  </si>
+  <si>
+    <t>Chongqing</t>
+  </si>
+  <si>
+    <t>E02572</t>
+  </si>
+  <si>
+    <t>Speciality Products</t>
+  </si>
+  <si>
+    <t>Caucasian</t>
+  </si>
+  <si>
+    <t>26-10-2006</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>E02832</t>
+  </si>
+  <si>
+    <t>27-09-2019</t>
+  </si>
+  <si>
+    <t>E01639</t>
+  </si>
+  <si>
+    <t>21-11-1995</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>E00644</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>24-01-2017</t>
+  </si>
+  <si>
+    <t>E01550</t>
+  </si>
+  <si>
+    <t>01-07-2020</t>
+  </si>
+  <si>
+    <t>E04332</t>
+  </si>
+  <si>
+    <t>16-05-2020</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>5/20/2021</t>
+  </si>
+  <si>
+    <t>E04533</t>
+  </si>
+  <si>
+    <t>25-01-2019</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>E03838</t>
+  </si>
+  <si>
+    <t>13-06-2018</t>
+  </si>
+  <si>
+    <t>E00591</t>
+  </si>
+  <si>
+    <t>Savannah King</t>
+  </si>
+  <si>
+    <t>Sr. Manager</t>
+  </si>
+  <si>
+    <t>11-02-2016</t>
+  </si>
+  <si>
+    <t>E03344</t>
+  </si>
+  <si>
+    <t>Camilla Rogers</t>
+  </si>
+  <si>
+    <t>21-10-2021</t>
+  </si>
+  <si>
+    <t>E00530</t>
+  </si>
+  <si>
+    <t>14-03-1999</t>
+  </si>
+  <si>
+    <t>E04239</t>
+  </si>
+  <si>
+    <t>10-06-2021</t>
+  </si>
+  <si>
+    <t>E03496</t>
+  </si>
+  <si>
+    <t>04-11-2017</t>
+  </si>
+  <si>
+    <t>E00549</t>
+  </si>
+  <si>
+    <t>13-03-2013</t>
+  </si>
+  <si>
+    <t>E00163</t>
+  </si>
+  <si>
+    <t>04-03-2002</t>
+  </si>
+  <si>
+    <t>E00884</t>
+  </si>
+  <si>
+    <t>Latino</t>
+  </si>
+  <si>
+    <t>01-12-2003</t>
+  </si>
+  <si>
+    <t>E04116</t>
+  </si>
+  <si>
+    <t>01-11-2013</t>
+  </si>
+  <si>
+    <t>E04625</t>
+  </si>
+  <si>
+    <t>Adam Dang</t>
+  </si>
+  <si>
+    <t>09-07-2002</t>
+  </si>
+  <si>
+    <t>empid</t>
+  </si>
+  <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>ename</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>bonus</t>
+  </si>
+  <si>
+    <t>range</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0"/>
+    <numFmt numFmtId="167" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -1290,13 +1525,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1309,8 +1545,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1464,11 +1706,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1544,12 +1806,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1579,14 +1838,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="24">
     <dxf>
       <font>
-        <b/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1602,15 +1903,21 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color rgb="FFC4C7C5"/>
         </left>
         <right style="medium">
           <color rgb="FFC4C7C5"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1631,6 +1938,22 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1813,9 +2136,252 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right/>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -1836,13 +2402,58 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
@@ -1890,21 +2501,37 @@
     <sortCondition ref="H1:H20"/>
   </sortState>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{245ABA7D-7ECE-4568-A31E-1E8B7C978F00}" name="Dates" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{245ABA7D-7ECE-4568-A31E-1E8B7C978F00}" name="Dates" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4F389F6-B9F3-44FE-A159-BC017026A4C9}" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4F389F6-B9F3-44FE-A159-BC017026A4C9}" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:E22" xr:uid="{A4F389F6-B9F3-44FE-A159-BC017026A4C9}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2A627C08-6C83-4E75-BCE6-1A6541F24982}" name="Date" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{E5035FA8-A98E-4E65-ACF0-DBE31FB290DB}" name="Category" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{831F6925-8AC2-4000-82BE-AAB751BED13C}" name="Sub-Category" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{693B7B40-96C4-4EA0-A9E3-23714B1370F2}" name="Amount" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{2387A324-DD9A-48CD-A65C-D45020B4CDE4}" name="Payment Mode" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{2A627C08-6C83-4E75-BCE6-1A6541F24982}" name="Date" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{E5035FA8-A98E-4E65-ACF0-DBE31FB290DB}" name="Category" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{831F6925-8AC2-4000-82BE-AAB751BED13C}" name="Sub-Category" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{693B7B40-96C4-4EA0-A9E3-23714B1370F2}" name="Amount" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{2387A324-DD9A-48CD-A65C-D45020B4CDE4}" name="Payment Mode" dataDxfId="13"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F489DC4B-2820-419C-A92D-64247B216257}" name="Table13" displayName="Table13" ref="A1:G22" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:G22" xr:uid="{F489DC4B-2820-419C-A92D-64247B216257}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{937F5DDA-0598-4BE6-A1E8-73B369B9D8CD}" name="Date" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{3866F29D-9648-44B7-841A-4C6C12E87E00}" name="Category" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{6F8C28E5-2B07-4F54-92B4-A22D8BFDE8BF}" name="Sub-Category" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{86BF265B-A19A-4F79-BC8E-CDDEF784FEED}" name="Amount" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{174730C7-474F-4DF3-A6E2-89A31E1AD901}" name="Payment Mode" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{34A9095F-F25F-4DA8-B0AF-43498479072F}" name="Date2" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{B06205D2-F51A-440E-A028-A8182D32AD55}" name="Sub-Category2" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2406,41 +3033,41 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3320,15 +3947,15 @@
     <row r="2" spans="1:18">
       <c r="A2" s="17">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
-      </c>
-      <c r="B2" s="32">
+        <v>46196</v>
+      </c>
+      <c r="B2" s="31">
         <f ca="1">NOW()</f>
-        <v>46195.516931134262</v>
+        <v>46196.025495833332</v>
       </c>
       <c r="C2">
         <f ca="1">DAY(B2)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <f ca="1">MONTH(B2)</f>
@@ -3340,35 +3967,35 @@
       </c>
       <c r="F2" s="17">
         <f ca="1">DATE(E2,D2,C2)</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="G2">
         <f ca="1">HOUR(B2)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <f ca="1">MINUTE(B2)</f>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I2">
         <f ca="1">SECOND(B2)</f>
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J2" s="17">
         <f ca="1">A2+3</f>
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="K2" s="17">
         <f ca="1">EDATE(A2,3)</f>
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="L2" s="17">
         <f ca="1">EDATE(A2,(12*3))</f>
-        <v>47291</v>
+        <v>47292</v>
       </c>
       <c r="M2" t="str">
         <f ca="1">TEXT(A2,"D")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2">
         <f ca="1">YEARFRAC(A2,L2)</f>
@@ -3384,7 +4011,7 @@
       </c>
       <c r="Q2" s="17">
         <f ca="1">EDATE(A2,11)</f>
-        <v>46529</v>
+        <v>46530</v>
       </c>
       <c r="R2" s="17">
         <f ca="1">EOMONTH(A2,0)</f>
@@ -3394,7 +4021,7 @@
     <row r="3" spans="1:18">
       <c r="M3" t="str">
         <f ca="1">TEXT(A2,"DD")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N3">
         <f ca="1">YEARFRAC(A2,K2)</f>
@@ -3402,26 +4029,26 @@
       </c>
       <c r="P3">
         <f ca="1">NETWORKDAYS.INTL(A2,L2)</f>
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="B4" s="33">
+      <c r="B4" s="32">
         <v>0.48888888888888887</v>
       </c>
       <c r="M4" t="str">
         <f ca="1">TEXT(A2,"DDD")</f>
-        <v>Mon</v>
+        <v>Tue</v>
       </c>
       <c r="Q4" s="17">
         <f ca="1">EDATE(A2,12*60)</f>
-        <v>68110</v>
+        <v>68111</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="M5" t="str">
         <f ca="1">TEXT(A2,"dddd")</f>
-        <v>Monday</v>
+        <v>Tuesday</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -3492,42 +4119,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.2" thickBot="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="33" t="s">
         <v>348</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="33" t="s">
         <v>349</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="33" t="s">
         <v>350</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="33" t="s">
         <v>351</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="33" t="s">
         <v>352</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="33" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.2" thickBot="1">
-      <c r="A2" s="35">
+      <c r="A2" s="34">
         <v>44935</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -3539,7 +4166,7 @@
       <c r="D2" s="2">
         <v>456</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="36" t="s">
         <v>218</v>
       </c>
       <c r="F2">
@@ -3568,7 +4195,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" thickBot="1">
-      <c r="A3" s="35">
+      <c r="A3" s="34">
         <v>44945</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -3580,12 +4207,12 @@
       <c r="D3" s="2">
         <v>26</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" thickBot="1">
-      <c r="A4" s="35">
+      <c r="A4" s="34">
         <v>44928</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -3597,7 +4224,7 @@
       <c r="D4" s="2">
         <v>890</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="36" t="s">
         <v>211</v>
       </c>
       <c r="F4">
@@ -3606,7 +4233,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="28.2" thickBot="1">
-      <c r="A5" s="35">
+      <c r="A5" s="34">
         <v>44950</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -3618,12 +4245,12 @@
       <c r="D5" s="2">
         <v>530</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="36" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="36">
+      <c r="A6" s="35">
         <v>44953</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -3635,12 +4262,12 @@
       <c r="D6" s="2">
         <v>300</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" thickBot="1">
-      <c r="A7" s="35">
+      <c r="A7" s="34">
         <v>44930</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -3652,7 +4279,7 @@
       <c r="D7" s="2">
         <v>257</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="36" t="s">
         <v>211</v>
       </c>
       <c r="F7">
@@ -3661,7 +4288,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="35">
+      <c r="A8" s="34">
         <v>44943</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -3673,12 +4300,12 @@
       <c r="D8" s="2">
         <v>100</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" thickBot="1">
-      <c r="A9" s="35">
+      <c r="A9" s="34">
         <v>44949</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -3690,7 +4317,7 @@
       <c r="D9" s="2">
         <v>56</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="36" t="s">
         <v>218</v>
       </c>
       <c r="F9">
@@ -3699,7 +4326,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="35">
+      <c r="A10" s="34">
         <v>44927</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -3711,12 +4338,12 @@
       <c r="D10" s="2">
         <v>30</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="36" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" thickBot="1">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>44952</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -3728,12 +4355,12 @@
       <c r="D11" s="2">
         <v>10</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="35">
+      <c r="A12" s="34">
         <v>44946</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -3745,12 +4372,12 @@
       <c r="D12" s="2">
         <v>780</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" thickBot="1">
-      <c r="A13" s="35">
+      <c r="A13" s="34">
         <v>44944</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -3762,12 +4389,12 @@
       <c r="D13" s="2">
         <v>120</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="35">
+      <c r="A14" s="34">
         <v>44932</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -3779,12 +4406,12 @@
       <c r="D14" s="2">
         <v>120</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" thickBot="1">
-      <c r="A15" s="35">
+      <c r="A15" s="34">
         <v>44941</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -3796,12 +4423,12 @@
       <c r="D15" s="2">
         <v>50</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="36" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="35">
+      <c r="A16" s="34">
         <v>44948</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -3813,12 +4440,12 @@
       <c r="D16" s="2">
         <v>1890</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" thickBot="1">
-      <c r="A17" s="35">
+      <c r="A17" s="34">
         <v>44947</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -3830,12 +4457,12 @@
       <c r="D17" s="2">
         <v>1000</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="36" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" thickBot="1">
-      <c r="A18" s="35">
+      <c r="A18" s="34">
         <v>44936</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -3847,12 +4474,12 @@
       <c r="D18" s="2">
         <v>16000</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" thickBot="1">
-      <c r="A19" s="35">
+      <c r="A19" s="34">
         <v>44955</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -3864,12 +4491,12 @@
       <c r="D19" s="2">
         <v>1650</v>
       </c>
-      <c r="E19" s="37" t="s">
+      <c r="E19" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" thickBot="1">
-      <c r="A20" s="35">
+      <c r="A20" s="34">
         <v>44956</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -3881,12 +4508,12 @@
       <c r="D20" s="2">
         <v>1074</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" thickBot="1">
-      <c r="A21" s="35">
+      <c r="A21" s="34">
         <v>44953</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -3898,24 +4525,24 @@
       <c r="D21" s="2">
         <v>10</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E21" s="36" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="41">
+      <c r="A22" s="40">
         <v>44938</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="41">
         <v>15</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="42" t="s">
         <v>211</v>
       </c>
     </row>
@@ -3924,6 +4551,2437 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4072F20-6EAA-4CE0-BE62-D85CC17D0C83}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A1" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A2" s="34">
+        <v>44935</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="2">
+        <v>456</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="F2" s="44">
+        <v>44928</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1">
+      <c r="A3" s="34">
+        <v>44945</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="2">
+        <v>26</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1">
+      <c r="A4" s="34">
+        <v>44928</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="2">
+        <v>890</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A5" s="34">
+        <v>44950</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="2">
+        <v>530</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1">
+      <c r="A6" s="35">
+        <v>44953</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D6" s="2">
+        <v>300</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1">
+      <c r="A7" s="34">
+        <v>44930</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="2">
+        <v>257</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1">
+      <c r="A8" s="34">
+        <v>44943</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="2">
+        <v>100</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A9" s="34">
+        <v>44949</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="2">
+        <v>56</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1">
+      <c r="A10" s="34">
+        <v>44927</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="2">
+        <v>30</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1">
+      <c r="A11" s="34">
+        <v>44952</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1">
+      <c r="A12" s="34">
+        <v>44946</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="2">
+        <v>780</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1">
+      <c r="A13" s="34">
+        <v>44944</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" s="2">
+        <v>120</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1">
+      <c r="A14" s="34">
+        <v>44932</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" s="2">
+        <v>120</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A15" s="34">
+        <v>44941</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="2">
+        <v>50</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1">
+      <c r="A16" s="34">
+        <v>44948</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1890</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1">
+      <c r="A17" s="34">
+        <v>44947</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1">
+      <c r="A18" s="34">
+        <v>44936</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D18" s="2">
+        <v>16000</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1">
+      <c r="A19" s="34">
+        <v>44955</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1650</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1">
+      <c r="A20" s="34">
+        <v>44956</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1074</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1">
+      <c r="A21" s="34">
+        <v>44953</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="2">
+        <v>10</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="40">
+        <v>44938</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="D22" s="41">
+        <v>15</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{CE19029F-20CB-4F1D-BF63-8F2F790A49B0}">
+      <formula1>44927</formula1>
+      <formula2>44957</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{45AC02FB-25D0-46DB-A7C8-43AAE78D0BDF}">
+      <formula1>2</formula1>
+      <formula2>20</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76AB953-3853-4820-A57D-5D55CB9D793A}">
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="28.8">
+      <c r="A1" s="45" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>283</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="H1" s="45" t="s">
+        <v>284</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="L1" s="45" t="s">
+        <v>286</v>
+      </c>
+      <c r="M1" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="N1" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="O1" s="52" t="s">
+        <v>426</v>
+      </c>
+      <c r="P1" s="50" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q1" s="50" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="46" t="s">
+        <v>364</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="H2" s="47">
+        <v>55</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="J2" s="48">
+        <v>141604</v>
+      </c>
+      <c r="K2" s="49">
+        <v>15</v>
+      </c>
+      <c r="L2" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="N2" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="O2" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="P2" s="46" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q2" s="51">
+        <f>VLOOKUP(P2,A2:N21,10,FALSE)</f>
+        <v>99975</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="46" t="s">
+        <v>370</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H3" s="47">
+        <v>59</v>
+      </c>
+      <c r="I3" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="J3" s="48">
+        <v>99975</v>
+      </c>
+      <c r="K3" s="49">
+        <v>0</v>
+      </c>
+      <c r="L3" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="M3" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="N3" s="46"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="46" t="s">
+        <v>375</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="H4" s="47">
+        <v>50</v>
+      </c>
+      <c r="I4" s="46" t="s">
+        <v>378</v>
+      </c>
+      <c r="J4" s="48">
+        <v>163099</v>
+      </c>
+      <c r="K4" s="49">
+        <v>20</v>
+      </c>
+      <c r="L4" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M4" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="N4" s="46"/>
+      <c r="Q4">
+        <f>VLOOKUP(O2,B2:N21,9,0)</f>
+        <v>119746</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="46" t="s">
+        <v>380</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="H5" s="47">
+        <v>26</v>
+      </c>
+      <c r="I5" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="J5" s="48">
+        <v>84913</v>
+      </c>
+      <c r="K5" s="49">
+        <v>7</v>
+      </c>
+      <c r="L5" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M5" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="N5" s="46"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H6" s="47">
+        <v>55</v>
+      </c>
+      <c r="I6" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="J6" s="48">
+        <v>95409</v>
+      </c>
+      <c r="K6" s="49">
+        <v>0</v>
+      </c>
+      <c r="L6" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M6" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="N6" s="46"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H7" s="47">
+        <v>57</v>
+      </c>
+      <c r="I7" s="46" t="s">
+        <v>387</v>
+      </c>
+      <c r="J7" s="48">
+        <v>50994</v>
+      </c>
+      <c r="K7" s="49">
+        <v>0</v>
+      </c>
+      <c r="L7" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="M7" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="N7" s="46"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="46" t="s">
+        <v>388</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="H8" s="47">
+        <v>27</v>
+      </c>
+      <c r="I8" s="46" t="s">
+        <v>389</v>
+      </c>
+      <c r="J8" s="48">
+        <v>119746</v>
+      </c>
+      <c r="K8" s="49">
+        <v>10</v>
+      </c>
+      <c r="L8" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M8" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="N8" s="46"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="H9" s="47">
+        <v>25</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>391</v>
+      </c>
+      <c r="J9" s="48">
+        <v>41336</v>
+      </c>
+      <c r="K9" s="49">
+        <v>0</v>
+      </c>
+      <c r="L9" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M9" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="N9" s="46" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="46" t="s">
+        <v>394</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="H10" s="47">
+        <v>29</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>395</v>
+      </c>
+      <c r="J10" s="48">
+        <v>113527</v>
+      </c>
+      <c r="K10" s="49">
+        <v>6</v>
+      </c>
+      <c r="L10" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M10" s="46" t="s">
+        <v>396</v>
+      </c>
+      <c r="N10" s="46"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="H11" s="47">
+        <v>34</v>
+      </c>
+      <c r="I11" s="46" t="s">
+        <v>398</v>
+      </c>
+      <c r="J11" s="48">
+        <v>77203</v>
+      </c>
+      <c r="K11" s="49">
+        <v>0</v>
+      </c>
+      <c r="L11" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M11" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="N11" s="46"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="46" t="s">
+        <v>399</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>401</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H12" s="47">
+        <v>36</v>
+      </c>
+      <c r="I12" s="46" t="s">
+        <v>402</v>
+      </c>
+      <c r="J12" s="48">
+        <v>157333</v>
+      </c>
+      <c r="K12" s="49">
+        <v>15</v>
+      </c>
+      <c r="L12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M12" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="N12" s="46"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="46" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>404</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="H13" s="47">
+        <v>27</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>405</v>
+      </c>
+      <c r="J13" s="48">
+        <v>109851</v>
+      </c>
+      <c r="K13" s="49">
+        <v>0</v>
+      </c>
+      <c r="L13" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M13" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="N13" s="46"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="46" t="s">
+        <v>406</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="H14" s="47">
+        <v>59</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>407</v>
+      </c>
+      <c r="J14" s="48">
+        <v>105086</v>
+      </c>
+      <c r="K14" s="49">
+        <v>9</v>
+      </c>
+      <c r="L14" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M14" s="46" t="s">
+        <v>396</v>
+      </c>
+      <c r="N14" s="46"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>323</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>292</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H15" s="47">
+        <v>51</v>
+      </c>
+      <c r="I15" s="46" t="s">
+        <v>409</v>
+      </c>
+      <c r="J15" s="48">
+        <v>146742</v>
+      </c>
+      <c r="K15" s="49">
+        <v>10</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="M15" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="N15" s="46"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H16" s="47">
+        <v>31</v>
+      </c>
+      <c r="I16" s="46" t="s">
+        <v>411</v>
+      </c>
+      <c r="J16" s="48">
+        <v>97078</v>
+      </c>
+      <c r="K16" s="49">
+        <v>0</v>
+      </c>
+      <c r="L16" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M16" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="N16" s="46"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G17" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H17" s="47">
+        <v>41</v>
+      </c>
+      <c r="I17" s="46" t="s">
+        <v>413</v>
+      </c>
+      <c r="J17" s="48">
+        <v>249270</v>
+      </c>
+      <c r="K17" s="49">
+        <v>30</v>
+      </c>
+      <c r="L17" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M17" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="N17" s="46"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="46" t="s">
+        <v>414</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="H18" s="47">
+        <v>65</v>
+      </c>
+      <c r="I18" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="J18" s="48">
+        <v>175837</v>
+      </c>
+      <c r="K18" s="49">
+        <v>20</v>
+      </c>
+      <c r="L18" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M18" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="N18" s="46"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>329</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>292</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="H19" s="47">
+        <v>64</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="J19" s="48">
+        <v>154828</v>
+      </c>
+      <c r="K19" s="49">
+        <v>13</v>
+      </c>
+      <c r="L19" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M19" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="N19" s="46"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="46" t="s">
+        <v>419</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="H20" s="47">
+        <v>64</v>
+      </c>
+      <c r="I20" s="46" t="s">
+        <v>420</v>
+      </c>
+      <c r="J20" s="48">
+        <v>186503</v>
+      </c>
+      <c r="K20" s="49">
+        <v>24</v>
+      </c>
+      <c r="L20" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M20" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="N20" s="46"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="46" t="s">
+        <v>421</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>422</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G21" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H21" s="47">
+        <v>45</v>
+      </c>
+      <c r="I21" s="46" t="s">
+        <v>423</v>
+      </c>
+      <c r="J21" s="48">
+        <v>166331</v>
+      </c>
+      <c r="K21" s="49">
+        <v>18</v>
+      </c>
+      <c r="L21" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="M21" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="N21" s="46"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535247DD-E1B5-4A88-9857-0C3FC055F33A}">
+  <dimension ref="A1:U21"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" s="45" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>364</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>380</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>388</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>394</v>
+      </c>
+      <c r="K1" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="L1" s="46" t="s">
+        <v>399</v>
+      </c>
+      <c r="M1" s="46" t="s">
+        <v>403</v>
+      </c>
+      <c r="N1" s="46" t="s">
+        <v>406</v>
+      </c>
+      <c r="O1" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="P1" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q1" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="R1" s="46" t="s">
+        <v>414</v>
+      </c>
+      <c r="S1" s="46" t="s">
+        <v>416</v>
+      </c>
+      <c r="T1" s="46" t="s">
+        <v>419</v>
+      </c>
+      <c r="U1" s="46" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="28.8">
+      <c r="A2" s="45" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="J2" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="K2" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="L2" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>404</v>
+      </c>
+      <c r="N2" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="O2" s="46" t="s">
+        <v>323</v>
+      </c>
+      <c r="P2" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q2" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="R2" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="S2" s="46" t="s">
+        <v>329</v>
+      </c>
+      <c r="T2" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="U2" s="46" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="I3" s="46" t="s">
+        <v>313</v>
+      </c>
+      <c r="J3" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="K3" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="L3" s="46" t="s">
+        <v>401</v>
+      </c>
+      <c r="M3" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="N3" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="O3" s="46" t="s">
+        <v>292</v>
+      </c>
+      <c r="P3" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q3" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="R3" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="S3" s="46" t="s">
+        <v>292</v>
+      </c>
+      <c r="T3" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="U3" s="46" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="28.8">
+      <c r="A4" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="I4" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="J4" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="K4" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="L4" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="M4" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="N4" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="O4" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="P4" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q4" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="R4" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="S4" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="T4" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="U4" s="46" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="28.8">
+      <c r="A5" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="H5" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="I5" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="J5" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="K5" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="L5" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="M5" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="N5" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="O5" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="P5" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q5" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="R5" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="S5" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="T5" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="U5" s="46" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="45" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="H6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="I6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="J6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="K6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="L6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="M6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="N6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="O6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="P6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="R6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="S6" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="T6" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="U6" s="46" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="H7" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="I7" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="J7" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="K7" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="L7" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="M7" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="N7" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="O7" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="P7" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q7" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="R7" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="S7" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="T7" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="U7" s="46" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="45" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" s="47">
+        <v>55</v>
+      </c>
+      <c r="C8" s="47">
+        <v>59</v>
+      </c>
+      <c r="D8" s="47">
+        <v>50</v>
+      </c>
+      <c r="E8" s="47">
+        <v>26</v>
+      </c>
+      <c r="F8" s="47">
+        <v>55</v>
+      </c>
+      <c r="G8" s="47">
+        <v>57</v>
+      </c>
+      <c r="H8" s="47">
+        <v>27</v>
+      </c>
+      <c r="I8" s="47">
+        <v>25</v>
+      </c>
+      <c r="J8" s="47">
+        <v>29</v>
+      </c>
+      <c r="K8" s="47">
+        <v>34</v>
+      </c>
+      <c r="L8" s="47">
+        <v>36</v>
+      </c>
+      <c r="M8" s="47">
+        <v>27</v>
+      </c>
+      <c r="N8" s="47">
+        <v>59</v>
+      </c>
+      <c r="O8" s="47">
+        <v>51</v>
+      </c>
+      <c r="P8" s="47">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="47">
+        <v>41</v>
+      </c>
+      <c r="R8" s="47">
+        <v>65</v>
+      </c>
+      <c r="S8" s="47">
+        <v>64</v>
+      </c>
+      <c r="T8" s="47">
+        <v>64</v>
+      </c>
+      <c r="U8" s="47">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>378</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>387</v>
+      </c>
+      <c r="H9" s="46" t="s">
+        <v>389</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>391</v>
+      </c>
+      <c r="J9" s="46" t="s">
+        <v>395</v>
+      </c>
+      <c r="K9" s="46" t="s">
+        <v>398</v>
+      </c>
+      <c r="L9" s="46" t="s">
+        <v>402</v>
+      </c>
+      <c r="M9" s="46" t="s">
+        <v>405</v>
+      </c>
+      <c r="N9" s="46" t="s">
+        <v>407</v>
+      </c>
+      <c r="O9" s="46" t="s">
+        <v>409</v>
+      </c>
+      <c r="P9" s="46" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q9" s="46" t="s">
+        <v>413</v>
+      </c>
+      <c r="R9" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="S9" s="46" t="s">
+        <v>418</v>
+      </c>
+      <c r="T9" s="46" t="s">
+        <v>420</v>
+      </c>
+      <c r="U9" s="46" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="28.8">
+      <c r="A10" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="B10" s="48">
+        <v>141604</v>
+      </c>
+      <c r="C10" s="48">
+        <v>99975</v>
+      </c>
+      <c r="D10" s="48">
+        <v>163099</v>
+      </c>
+      <c r="E10" s="48">
+        <v>84913</v>
+      </c>
+      <c r="F10" s="48">
+        <v>95409</v>
+      </c>
+      <c r="G10" s="48">
+        <v>50994</v>
+      </c>
+      <c r="H10" s="48">
+        <v>119746</v>
+      </c>
+      <c r="I10" s="48">
+        <v>41336</v>
+      </c>
+      <c r="J10" s="48">
+        <v>113527</v>
+      </c>
+      <c r="K10" s="48">
+        <v>77203</v>
+      </c>
+      <c r="L10" s="48">
+        <v>157333</v>
+      </c>
+      <c r="M10" s="48">
+        <v>109851</v>
+      </c>
+      <c r="N10" s="48">
+        <v>105086</v>
+      </c>
+      <c r="O10" s="48">
+        <v>146742</v>
+      </c>
+      <c r="P10" s="48">
+        <v>97078</v>
+      </c>
+      <c r="Q10" s="48">
+        <v>249270</v>
+      </c>
+      <c r="R10" s="48">
+        <v>175837</v>
+      </c>
+      <c r="S10" s="48">
+        <v>154828</v>
+      </c>
+      <c r="T10" s="48">
+        <v>186503</v>
+      </c>
+      <c r="U10" s="48">
+        <v>166331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" s="49">
+        <v>15</v>
+      </c>
+      <c r="C11" s="49">
+        <v>0</v>
+      </c>
+      <c r="D11" s="49">
+        <v>20</v>
+      </c>
+      <c r="E11" s="49">
+        <v>7</v>
+      </c>
+      <c r="F11" s="49">
+        <v>0</v>
+      </c>
+      <c r="G11" s="49">
+        <v>0</v>
+      </c>
+      <c r="H11" s="49">
+        <v>10</v>
+      </c>
+      <c r="I11" s="49">
+        <v>0</v>
+      </c>
+      <c r="J11" s="49">
+        <v>6</v>
+      </c>
+      <c r="K11" s="49">
+        <v>0</v>
+      </c>
+      <c r="L11" s="49">
+        <v>15</v>
+      </c>
+      <c r="M11" s="49">
+        <v>0</v>
+      </c>
+      <c r="N11" s="49">
+        <v>9</v>
+      </c>
+      <c r="O11" s="49">
+        <v>10</v>
+      </c>
+      <c r="P11" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="49">
+        <v>30</v>
+      </c>
+      <c r="R11" s="49">
+        <v>20</v>
+      </c>
+      <c r="S11" s="49">
+        <v>13</v>
+      </c>
+      <c r="T11" s="49">
+        <v>24</v>
+      </c>
+      <c r="U11" s="49">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="45" t="s">
+        <v>286</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="H12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="I12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="J12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="K12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="L12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="M12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="N12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="O12" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="P12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="R12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="S12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="T12" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="U12" s="46" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="H13" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>396</v>
+      </c>
+      <c r="K13" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="L13" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="M13" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="N13" s="46" t="s">
+        <v>396</v>
+      </c>
+      <c r="O13" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="P13" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q13" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="R13" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="S13" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="T13" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="U13" s="46" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46" t="s">
+        <v>393</v>
+      </c>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="46" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21">
+        <f>HLOOKUP(B20,B1:U14,10,FALSE)</f>
+        <v>163099</v>
+      </c>
+      <c r="C21">
+        <f>HLOOKUP(B1,B1:U14,10,FALSE)</f>
+        <v>141604</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014E3185-38BF-452B-B145-5F59ABDA6F73}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="48">
+        <v>141604</v>
+      </c>
+      <c r="C2" s="54">
+        <f>LOOKUP(B2,$E$2:$F$5)</f>
+        <v>0.15</v>
+      </c>
+      <c r="E2" s="20">
+        <v>50000</v>
+      </c>
+      <c r="F2" s="54">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="48">
+        <v>99975</v>
+      </c>
+      <c r="C3" s="54">
+        <f t="shared" ref="C3:C6" si="0">LOOKUP(B3,$E$2:$F$5)</f>
+        <v>0.1</v>
+      </c>
+      <c r="E3">
+        <v>80000</v>
+      </c>
+      <c r="F3" s="54">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" s="48">
+        <v>163099</v>
+      </c>
+      <c r="C4" s="54">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="E4">
+        <v>100000</v>
+      </c>
+      <c r="F4" s="54">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="48">
+        <v>84913</v>
+      </c>
+      <c r="C5" s="54">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="E5">
+        <v>150000</v>
+      </c>
+      <c r="F5" s="54">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" s="48">
+        <v>95409</v>
+      </c>
+      <c r="C6" s="54">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5749,7 +8807,7 @@
     <row r="1" spans="1:1">
       <c r="A1" s="18">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -6223,7 +9281,7 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B826AE99-B430-41F9-A794-0F8799894DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F663C25-01A7-4714-9691-623CB7505111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="10" activeTab="15" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="10" activeTab="16" xr2:uid="{E7031663-74BC-4F41-B481-C8EF92FE4458}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash Fill" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="Vlookup" sheetId="15" r:id="rId14"/>
     <sheet name="Hlookup" sheetId="17" r:id="rId15"/>
     <sheet name="Lookup" sheetId="18" r:id="rId16"/>
+    <sheet name="xlookup" sheetId="19" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Filteering!$A$1:$E$20</definedName>
@@ -152,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="431">
   <si>
     <t>Mohan</t>
   </si>
@@ -1442,6 +1443,9 @@
   </si>
   <si>
     <t>range</t>
+  </si>
+  <si>
+    <t>job title</t>
   </si>
 </sst>
 </file>
@@ -1866,10 +1870,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3033,41 +3037,41 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3951,7 +3955,7 @@
       </c>
       <c r="B2" s="31">
         <f ca="1">NOW()</f>
-        <v>46196.025495833332</v>
+        <v>46196.369690740743</v>
       </c>
       <c r="C2">
         <f ca="1">DAY(B2)</f>
@@ -3971,15 +3975,15 @@
       </c>
       <c r="G2">
         <f ca="1">HOUR(B2)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <f ca="1">MINUTE(B2)</f>
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I2">
         <f ca="1">SECOND(B2)</f>
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J2" s="17">
         <f ca="1">A2+3</f>
@@ -6903,14 +6907,14 @@
       <c r="B2" s="48">
         <v>141604</v>
       </c>
-      <c r="C2" s="54">
+      <c r="C2" s="53">
         <f>LOOKUP(B2,$E$2:$F$5)</f>
         <v>0.15</v>
       </c>
       <c r="E2" s="20">
         <v>50000</v>
       </c>
-      <c r="F2" s="54">
+      <c r="F2" s="53">
         <v>0.05</v>
       </c>
     </row>
@@ -6921,14 +6925,14 @@
       <c r="B3" s="48">
         <v>99975</v>
       </c>
-      <c r="C3" s="54">
+      <c r="C3" s="53">
         <f t="shared" ref="C3:C6" si="0">LOOKUP(B3,$E$2:$F$5)</f>
         <v>0.1</v>
       </c>
       <c r="E3">
         <v>80000</v>
       </c>
-      <c r="F3" s="54">
+      <c r="F3" s="53">
         <v>0.1</v>
       </c>
     </row>
@@ -6939,14 +6943,14 @@
       <c r="B4" s="48">
         <v>163099</v>
       </c>
-      <c r="C4" s="54">
+      <c r="C4" s="53">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="E4">
         <v>100000</v>
       </c>
-      <c r="F4" s="54">
+      <c r="F4" s="53">
         <v>0.15</v>
       </c>
     </row>
@@ -6957,14 +6961,14 @@
       <c r="B5" s="48">
         <v>84913</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="53">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="E5">
         <v>150000</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="53">
         <v>0.2</v>
       </c>
     </row>
@@ -6975,13 +6979,74 @@
       <c r="B6" s="48">
         <v>95409</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="53">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314CDDF0-D833-48F4-A520-012E02EB3080}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" t="str">
+        <f>_xlfn.XLOOKUP(A2,Vlookup!A2:A21,Vlookup!C2:C21)</f>
+        <v>Analyst</v>
+      </c>
+      <c r="C2" t="str">
+        <f>_xlfn.XLOOKUP(Vlookup!D17,Vlookup!D2:D21,Vlookup!B2:B21)</f>
+        <v>Isabella Xi</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="D5" t="str">
+        <f>_xlfn.XLOOKUP(Hlookup!B3,Hlookup!B3:U3,Hlookup!B2:U2)</f>
+        <v>Emily Davis</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="46" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7" t="str">
+        <f>_xlfn.XLOOKUP(A7,Vlookup!A2:A21,Vlookup!C2:C21)</f>
+        <v>Director</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66312B91-AF0F-4BFB-A93A-AF82087B0F68}">
+          <x14:formula1>
+            <xm:f>Vlookup!$A$2:$A$21</xm:f>
+          </x14:formula1>
+          <xm:sqref>A7</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
